--- a/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA70"/>
+  <dimension ref="A1:AF70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="3" min="1" max="1"/>
@@ -667,6 +667,31 @@
           <t>Tier</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>AltEffect</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>AltCalcBase</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>AltCalcValue</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>AltCondN</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>AltLimit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -731,75 +756,100 @@
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>SkillTarget</t>
+        </is>
+      </c>
+      <c r="O2" s="12" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="P2" s="12" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N2" s="12" t="inlineStr">
-        <is>
-          <t>SkillTarget</t>
-        </is>
-      </c>
-      <c r="O2" s="12" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="R2" s="12" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="P2" s="12" t="inlineStr">
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="Q2" s="12" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="U2" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="R2" s="12" t="inlineStr">
+      <c r="V2" s="10" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="S2" s="12" t="inlineStr">
+      <c r="W2" s="10" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T2" s="12" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="U2" s="9" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>SkillStatus</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="V2" s="10" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>SkillEffect</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>CalcBase</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="X2" s="12" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="Y2" s="12" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="Z2" s="12" t="inlineStr">
-        <is>
-          <t>SkillStatus</t>
-        </is>
-      </c>
-      <c r="AA2" s="12" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -939,6 +989,31 @@
       <c r="AA3" s="12" t="inlineStr">
         <is>
           <t>武学品阶(1入门/2精良/3上乘/4绝学);敌方按层限制可用上限 TierCap=min(4,1+(层-1)/10)</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>副效果词(0=无)。一张卡的第二档，条件沿用本行触发时机/CondType</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>副效果数值基准</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>副效果数值(与 CalcValue 同口径)</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>副效果需求次数(条件=1次数)</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>副效果每场释放次数上限(0=不限)</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3442,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>受击每2次，护盾=气血上限8%</t>
+          <t>受击每次，护盾=气血上限1.5%</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
@@ -3380,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
@@ -3398,7 +3473,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -3451,7 +3526,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>受击每4次，反弹=累计受击伤害50%</t>
+          <t>受击每6次，反弹=累计受击伤害50%</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
@@ -3464,7 +3539,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
@@ -3535,7 +3610,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>受击每3次，治疗=气血上限12%</t>
+          <t>受击每次，治疗=气血上限1.5%</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
@@ -3548,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>0</v>
@@ -3566,7 +3641,7 @@
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>12</v>
+        <v>1.5</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>0</v>
@@ -3619,7 +3694,7 @@
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>受击每5次，召唤替身傀儡</t>
+          <t>受击每6次，召唤替身傀儡</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
@@ -3632,7 +3707,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -3708,7 +3783,7 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>受击每6次，护盾=气血上限24%</t>
+          <t>受击每次，护盾=气血上限1%；受击每9次，护盾=气血上限24%（每场1次）</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
@@ -3721,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -3739,46 +3814,61 @@
         <v>2</v>
       </c>
       <c r="M37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="S37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD37" t="n">
         <v>24</v>
       </c>
-      <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="12" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="W37" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA37" s="12" t="n">
-        <v>2</v>
+      <c r="AE37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -3792,7 +3882,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>受击30%，0.8×反伤</t>
+          <t>受击24%，0.8×反伤</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
@@ -3808,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>0</v>
@@ -3876,7 +3966,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>受击25%，0.5×反伤</t>
+          <t>受击20%，0.5×反伤</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
@@ -3892,7 +3982,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -3960,7 +4050,7 @@
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>受击15%，自身W+12(10s)</t>
+          <t>受击12%，自身W+12(10s)</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">
@@ -3976,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
@@ -4044,7 +4134,7 @@
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>受击20%，自身W−10(10s，下限1)</t>
+          <t>受击16%，自身W−10(10s，下限1)</t>
         </is>
       </c>
       <c r="D41" s="12" t="n">
@@ -4060,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
@@ -4128,7 +4218,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>受击10%，攻击者SPD−15%(10s)</t>
+          <t>受击8%，攻击者SPD−15%(10s)</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
@@ -4144,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>
@@ -4810,7 +4900,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>受击每3次，召唤纸人(替死)</t>
+          <t>受击每5次，召唤纸人(替死)</t>
         </is>
       </c>
       <c r="D50" s="12" t="n">
@@ -4823,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
@@ -5156,7 +5246,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>受击每2次，己方血最少者W−10、自身W+10(10s)[待实装:双目标]</t>
+          <t>受击每3次，己方血最少者W−10、自身W+10(10s)[待实装:双目标]</t>
         </is>
       </c>
       <c r="D54" s="12" t="n">
@@ -5169,7 +5259,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
@@ -6332,7 +6422,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>受击30%，完全闪避该次攻击</t>
+          <t>受击24%，完全闪避该次攻击</t>
         </is>
       </c>
       <c r="D68" s="12" t="n">
@@ -6348,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I68" s="12" t="n">
         <v>0</v>

--- a/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
@@ -667,27 +667,27 @@
           <t>Tier</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="0" t="inlineStr">
         <is>
           <t>AltEffect</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="0" t="inlineStr">
         <is>
           <t>AltCalcBase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="0" t="inlineStr">
         <is>
           <t>AltCalcValue</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="0" t="inlineStr">
         <is>
           <t>AltCondN</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="0" t="inlineStr">
         <is>
           <t>AltLimit</t>
         </is>
@@ -829,27 +829,27 @@
           <t>int</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" s="0" t="inlineStr">
         <is>
           <t>SkillEffect</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC2" s="0" t="inlineStr">
         <is>
           <t>CalcBase</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="0" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -991,27 +991,27 @@
           <t>武学品阶(1入门/2精良/3上乘/4绝学);敌方按层限制可用上限 TierCap=min(4,1+(层-1)/10)</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" s="0" t="inlineStr">
         <is>
           <t>副效果词(0=无)。一张卡的第二档，条件沿用本行触发时机/CondType</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC3" s="0" t="inlineStr">
         <is>
           <t>副效果数值基准</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" s="0" t="inlineStr">
         <is>
           <t>副效果数值(与 CalcValue 同口径)</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE3" s="0" t="inlineStr">
         <is>
           <t>副效果需求次数(条件=1次数)</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" s="0" t="inlineStr">
         <is>
           <t>副效果每场释放次数上限(0=不限)</t>
         </is>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>受击每次，护盾=气血上限1.5%</t>
+          <t>受击每3次，护盾=气血上限4.5%</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
@@ -3455,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>受击每次，治疗=气血上限1.5%</t>
+          <t>受击每5次，治疗=气血上限6%</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
@@ -3623,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>0</v>
@@ -3641,7 +3641,7 @@
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>0</v>
@@ -3855,19 +3855,19 @@
       <c r="AA37" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="AB37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD37" t="n">
+      <c r="AB37" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC37" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD37" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AE37" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AF37" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，2.0×伤害</t>
+          <t>行动每3次，2.4×伤害</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -1121,7 +1121,7 @@
         <v>1</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="N5" s="12" t="n">
         <v>1</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，3.5×伤害(不能普攻)</t>
+          <t>行动每4次，4.2×伤害(不能普攻)</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
@@ -1205,7 +1205,7 @@
         <v>1</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="N6" s="12" t="n">
         <v>1</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>行动每2次，1.2×伤害，打最高权重</t>
+          <t>行动每2次，1.44×伤害，打最高权重</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -1289,7 +1289,7 @@
         <v>1</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="N7" s="12" t="n">
         <v>4</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>行动每5次，1.0×伤害，敌方全体</t>
+          <t>行动每5次，1.2×伤害，敌方全体</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
@@ -1373,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="M8" s="12" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N8" s="12" t="n">
         <v>5</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，2.5×伤害，打最高权重</t>
+          <t>行动每3次，3.0×伤害，打最高权重</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>4</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，1.0×伤害×3段(同目标)[待实装:多段]</t>
+          <t>行动每3次，1.2×伤害×3段(同目标)[待实装:多段]</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
@@ -1709,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>1</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，HP&lt;50%时4.0×否则1.5×[待实装:条件倍率]</t>
+          <t>行动每4次，HP&lt;50%时4.0×否则1.8×[待实装:条件倍率]</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
@@ -1793,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>1</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，2.8×伤害并清除目标护盾[待实装:清盾]</t>
+          <t>行动每4次，3.36×伤害并清除目标护盾[待实装:清盾]</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
@@ -1961,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>4</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，3.2×真伤，自损当前HP5%[待实装:自损]</t>
+          <t>行动每4次，3.84×真伤，自损当前HP5%[待实装:自损]</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>5</v>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>行动每6次，3.5×伤害，敌方全体(不能普攻)</t>
+          <t>行动每6次，4.2×伤害，敌方全体(不能普攻)</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
@@ -2213,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>5</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>行动30%，1.5×伤害，打敌方血最少</t>
+          <t>行动30%，1.8×伤害，打敌方血最少</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
@@ -2297,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>行动25%，1.8×伤害</t>
+          <t>行动25%，2.16×伤害</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
@@ -2381,7 +2381,7 @@
         <v>1</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>行动20%，0.8×伤害，敌方全体</t>
+          <t>行动20%，0.96×伤害，敌方全体</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
@@ -2465,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>5</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>行动15%，4.0×伤害(不能普攻)</t>
+          <t>行动15%，4.8×伤害(不能普攻)</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
@@ -2549,7 +2549,7 @@
         <v>1</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>1</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>行动35%，追加0.6×伤害</t>
+          <t>行动35%，追加0.72×伤害</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
@@ -2633,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>连击时25%，2.0×伤害</t>
+          <t>连击时25%，2.4×伤害</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
@@ -2801,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>1</v>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>行动30%，1.2×伤害并吸血50%</t>
+          <t>行动30%，1.44×伤害并吸血50%</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>行动20%，2.0×真伤+沉默5s(打最高权重[破防破招])</t>
+          <t>行动20%，2.4×真伤+沉默5s(打最高权重[破防破招])</t>
         </is>
       </c>
       <c r="D27" s="12" t="n">
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>4</v>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>行动30%，追加0.8×伤害(随机另一目标)</t>
+          <t>行动30%，追加0.96×伤害(随机另一目标)</t>
         </is>
       </c>
       <c r="D28" s="12" t="n">
@@ -3053,7 +3053,7 @@
         <v>1</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>1</v>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>受击每5次，治疗=气血上限6%</t>
+          <t>受击每5次，治疗=气血上限7.5%</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
@@ -3641,7 +3641,7 @@
         <v>2</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>受击24%，0.8×反伤</t>
+          <t>受击24%，0.96×反伤</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
@@ -3913,7 +3913,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>1</v>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>受击20%，0.5×反伤</t>
+          <t>受击20%，0.6×反伤</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
@@ -3997,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>1</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>HP&lt;15%，5.0×真伤(全体)，自损当前HP50%[待实装:自损]</t>
+          <t>HP&lt;15%，6.0×真伤(全体)，自损当前HP50%[待实装:自损]</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
@@ -4501,7 +4501,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>5</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>行动每8次，1.0×伤害，重放长尾(不能普攻)</t>
+          <t>行动每8次，1.2×伤害，重放长尾(不能普攻)</t>
         </is>
       </c>
       <c r="D61" s="12" t="n">
@@ -5865,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>1</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，0.6×伤害，重放</t>
+          <t>行动每3次，0.72×伤害，重放</t>
         </is>
       </c>
       <c r="D62" s="12" t="n">
@@ -5949,7 +5949,7 @@
         <v>1</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>1</v>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，0.8×伤害，重放(独立索敌)</t>
+          <t>行动每4次，0.96×伤害，重放(独立索敌)</t>
         </is>
       </c>
       <c r="D63" s="12" t="n">
@@ -6033,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>1</v>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>行动每5次，0.5×伤害，重放(独立索敌)</t>
+          <t>行动每5次，0.6×伤害，重放(独立索敌)</t>
         </is>
       </c>
       <c r="D64" s="12" t="n">
@@ -6117,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>1</v>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>行动每5次，0.6×伤害，重放(独立索敌)</t>
+          <t>行动每5次，0.72×伤害，重放(独立索敌)</t>
         </is>
       </c>
       <c r="D67" s="12" t="n">
@@ -6369,7 +6369,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>1</v>

--- a/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
+++ b/addons/TinyTools/ConfigGenerator/SkillConfig.xlsx
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，2.4×伤害</t>
+          <t>行动每3次，2.4×伤害（外功）</t>
         </is>
       </c>
       <c r="D5" s="12" t="n">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，4.2×伤害(不能普攻)</t>
+          <t>行动每4次，4.2×伤害（外功）(不能普攻)</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>行动每2次，1.44×伤害，打最高权重</t>
+          <t>行动每2次，1.44×伤害（外功），打最高权重</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>行动每5次，1.2×伤害，敌方全体</t>
+          <t>行动每5次，1.2×伤害（外功），敌方全体</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，3.0×伤害，打最高权重</t>
+          <t>行动每3次，3.0×伤害（外功），打最高权重</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，1.2×伤害×3段(同目标)[待实装:多段]</t>
+          <t>行动每3次，1.2×伤害（外功）×3段(同目标)[待实装:多段]</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，HP&lt;50%时4.0×否则1.8×[待实装:条件倍率]</t>
+          <t>行动每4次，HP&lt;50%时4.0×伤害（外功）否则1.8×伤害（外功）[待实装:条件倍率]</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>行动每5次，清空自身护盾转等量伤害(不能普攻)</t>
+          <t>行动每5次，清空自身护盾转等量内功伤害(不能普攻)</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，3.36×伤害并清除目标护盾[待实装:清盾]</t>
+          <t>行动每4次，3.36×伤害（外功）并清除目标护盾[待实装:清盾]</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，叠毒1层(每层每秒0.2×，不衰减，上限5)</t>
+          <t>行动每3次，叠毒6层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
@@ -2045,7 +2045,7 @@
         <v>3</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>1</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，3.84×真伤，自损当前HP5%[待实装:自损]</t>
+          <t>行动每4次，3.84×伤害（真伤）；另：自损气血上限5%（代价）</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
@@ -2169,6 +2169,21 @@
       </c>
       <c r="AA17" s="12" t="n">
         <v>4</v>
+      </c>
+      <c r="AB17" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC17" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2182,7 +2197,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>行动每6次，4.2×伤害，敌方全体(不能普攻)</t>
+          <t>行动每6次，4.2×伤害（外功），敌方全体(不能普攻)</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
@@ -2266,7 +2281,7 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>行动30%，1.8×伤害，打敌方血最少</t>
+          <t>行动30%，1.8×伤害（外功），打敌方血最少</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
@@ -2350,7 +2365,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>行动25%，2.16×伤害</t>
+          <t>行动25%，2.16×伤害（外功）</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
@@ -2434,7 +2449,7 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>行动20%，0.96×伤害，敌方全体</t>
+          <t>行动每5次，敌方全体各叠毒4层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
@@ -2444,28 +2459,28 @@
         <v>1</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>5</v>
@@ -2518,7 +2533,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>行动15%，4.8×伤害(不能普攻)</t>
+          <t>行动15%，4.8×伤害（外功）(不能普攻)</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
@@ -2602,7 +2617,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>行动35%，追加0.72×伤害</t>
+          <t>行动35%，追加0.72×伤害（外功）</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
@@ -2770,7 +2785,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>连击时25%，2.4×伤害</t>
+          <t>连击时25%，2.4×伤害（外功）</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
@@ -2854,7 +2869,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>行动30%，1.44×伤害并吸血50%</t>
+          <t>行动30%，1.44×伤害（内功）并吸血50%</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
@@ -2938,7 +2953,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>行动20%，2.4×真伤+沉默5s(打最高权重[破防破招])</t>
+          <t>行动20%，2.4×伤害（真伤）+沉默5s(打最高权重[破防破招])</t>
         </is>
       </c>
       <c r="D27" s="12" t="n">
@@ -3022,7 +3037,7 @@
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>行动30%，追加0.96×伤害(随机另一目标)</t>
+          <t>行动30%，追加0.96×伤害（外功）(随机另一目标)</t>
         </is>
       </c>
       <c r="D28" s="12" t="n">
@@ -3106,7 +3121,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>行动25%，灼烧(每秒0.25×，每跳衰减10%，10s)</t>
+          <t>行动25%，灼烧6层（每层1点/秒，被护盾吸收，10s）</t>
         </is>
       </c>
       <c r="D29" s="12" t="n">
@@ -3134,10 +3149,10 @@
         <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
@@ -3526,7 +3541,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>受击每6次，反弹=累计受击伤害50%给攻击者</t>
+          <t>受击每6次，反弹=累计受击伤害50%给攻击者（内功）</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
@@ -3783,7 +3798,7 @@
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>受击每次，护盾=气血上限1%；受击每9次，护盾=气血上限24%（每场1次）</t>
+          <t>受击每次，护盾=气血上限1%；受击每6次，护盾=气血上限21%（每场1次）</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
@@ -3862,10 +3877,10 @@
         <v>2</v>
       </c>
       <c r="AD37" s="0" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE37" s="0" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF37" s="0" t="n">
         <v>1</v>
@@ -3882,7 +3897,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>受击24%，0.96×反伤给攻击者</t>
+          <t>受击24%，0.96×反伤给攻击者（外功）</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
@@ -3966,7 +3981,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>受击20%，0.6×反伤给攻击者</t>
+          <t>受击每4次，引爆攻击者毒层（每层0.5×攻击，内功，引爆即清空）</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
@@ -3976,13 +3991,13 @@
         <v>2</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -3991,13 +4006,13 @@
         <v>2</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>6</v>
@@ -4470,7 +4485,7 @@
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>HP&lt;15%，6.0×真伤(全体)，自损当前HP50%[待实装:自损]</t>
+          <t>HP&lt;15%，6.0×伤害（真伤，全体）；另：自损气血上限50%（代价）</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
@@ -4541,6 +4556,21 @@
       </c>
       <c r="AA45" s="12" t="n">
         <v>4</v>
+      </c>
+      <c r="AB45" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC45" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD45" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5498,7 +5528,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>开战，己方全体持续治疗=气血上限2.0%/跳(2s)</t>
+          <t>开战，己方全体HoT 6层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D57" s="12" t="n">
@@ -5526,10 +5556,10 @@
         <v>20</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>5</v>
@@ -5834,7 +5864,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>行动每8次，1.2×伤害，重放长尾(不能普攻)</t>
+          <t>行动每6次，1.05×伤害（外功），重放长尾(不能普攻)</t>
         </is>
       </c>
       <c r="D61" s="12" t="n">
@@ -5847,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H61" s="12" t="n">
         <v>0</v>
@@ -5865,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>1</v>
@@ -5918,7 +5948,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>行动每3次，0.72×伤害，重放</t>
+          <t>行动每4次，叠毒4层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D62" s="12" t="n">
@@ -5931,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>0</v>
@@ -5940,16 +5970,16 @@
         <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>1</v>
@@ -6002,7 +6032,7 @@
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>行动每4次，0.96×伤害，重放(独立索敌)</t>
+          <t>行动每4次，0.96×伤害（外功），重放(独立索敌)</t>
         </is>
       </c>
       <c r="D63" s="12" t="n">
@@ -6086,7 +6116,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>行动每5次，0.6×伤害，重放(独立索敌)</t>
+          <t>行动每5次，0.6×伤害（外功），重放(独立索敌)</t>
         </is>
       </c>
       <c r="D64" s="12" t="n">
@@ -6254,7 +6284,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>行动每7次，污染敌方两张武学[待实装:污染]</t>
+          <t>行动每5次，引爆目标毒层（每层0.9×攻击，内功，引爆即清空）</t>
         </is>
       </c>
       <c r="D66" s="12" t="n">
@@ -6267,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>0</v>
@@ -6276,19 +6306,19 @@
         <v>0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" s="12" t="b">
         <v>0</v>
@@ -6321,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="Z66" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA66" s="12" t="n">
         <v>3</v>
@@ -6338,7 +6368,7 @@
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>行动每5次，0.72×伤害，重放(独立索敌)</t>
+          <t>行动每5次，0.72×伤害（外功），重放(独立索敌)</t>
         </is>
       </c>
       <c r="D67" s="12" t="n">
@@ -6674,7 +6704,7 @@
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>龟寿功</t>
+          <t>听剑录</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -6758,12 +6788,12 @@
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>养血诀</t>
+          <t>藏刀诀</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>被动，气血上限+6%</t>
+          <t>被动，气血上限+6%；开战，自身护盾=气血上限6%</t>
         </is>
       </c>
       <c r="D72" s="0" t="n">
@@ -6834,6 +6864,21 @@
       </c>
       <c r="AA72" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="AB72" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC72" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD72" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6842,7 +6887,7 @@
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>铁骨功</t>
+          <t>浑元桩</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -6926,12 +6971,12 @@
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>培元功</t>
+          <t>柔云诀</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>被动，气血上限+10%</t>
+          <t>被动，气血上限+10%；开战，己方全体HoT 2层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D74" s="0" t="n">
@@ -7002,6 +7047,21 @@
       </c>
       <c r="AA74" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="AB74" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC74" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD74" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7010,12 +7070,12 @@
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>厚土诀</t>
+          <t>马步诀</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>被动，气血上限+15%</t>
+          <t>被动，气血上限+15%；开战，自身受击权重+6（站桩吃招）</t>
         </is>
       </c>
       <c r="D75" s="0" t="n">
@@ -7086,6 +7146,21 @@
       </c>
       <c r="AA75" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB75" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC75" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD75" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -7094,12 +7169,12 @@
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>沧桑体</t>
+          <t>韧骨篇</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>被动，气血上限+15%</t>
+          <t>被动，气血上限+15%；开战，自身护盾=气血上限8%</t>
         </is>
       </c>
       <c r="D76" s="0" t="n">
@@ -7170,6 +7245,21 @@
       </c>
       <c r="AA76" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB76" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC76" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD76" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE76" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -7178,12 +7268,12 @@
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>固元功</t>
+          <t>凝神诀</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>被动，气血上限+15%</t>
+          <t>被动，气血上限+15%；开战，自身攻击+8%</t>
         </is>
       </c>
       <c r="D77" s="0" t="n">
@@ -7254,6 +7344,21 @@
       </c>
       <c r="AA77" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB77" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC77" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD77" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE77" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -7262,12 +7367,12 @@
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>养神篇</t>
+          <t>缩地功</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>被动，气血上限+22%</t>
+          <t>被动，气血上限+22%；开战，自身速度+15%</t>
         </is>
       </c>
       <c r="D78" s="0" t="n">
@@ -7338,6 +7443,21 @@
       </c>
       <c r="AA78" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB78" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC78" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD78" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -7346,12 +7466,12 @@
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>驻颜经</t>
+          <t>生生诀</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>被动，气血上限+22%</t>
+          <t>被动，气血上限+22%；开战，自身HoT 8层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D79" s="0" t="n">
@@ -7422,6 +7542,21 @@
       </c>
       <c r="AA79" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB79" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC79" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD79" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE79" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -7430,7 +7565,7 @@
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>不坏身</t>
+          <t>蚀心篇</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -7514,7 +7649,7 @@
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>锐金诀</t>
+          <t>八卦桩</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -7598,12 +7733,12 @@
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>破锋篇</t>
+          <t>金刚坐</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>被动，攻击+5%</t>
+          <t>被动，攻击+5%；开战，给随机敌人挂1层破绽（每层：下一次受击受伤+40%）</t>
         </is>
       </c>
       <c r="D82" s="0" t="n">
@@ -7674,6 +7809,21 @@
       </c>
       <c r="AA82" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="AB82" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC82" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -7682,7 +7832,7 @@
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>淬锋功</t>
+          <t>狼顾功</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -7767,12 +7917,12 @@
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>锋锐诀</t>
+          <t>养锋诀</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>被动，攻击+8%</t>
+          <t>被动，攻击+8%；开战，自身速度+8%（整场）</t>
         </is>
       </c>
       <c r="D84" s="0" t="n">
@@ -7843,6 +7993,21 @@
       </c>
       <c r="AA84" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="AB84" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC84" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD84" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7851,12 +8016,12 @@
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>砺剑篇</t>
+          <t>磨刃篇</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>被动，攻击+12%</t>
+          <t>被动，攻击+12%；开战，自身速度+8%（刃快先至）</t>
         </is>
       </c>
       <c r="D85" s="0" t="n">
@@ -7927,6 +8092,21 @@
       </c>
       <c r="AA85" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB85" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC85" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD85" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE85" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF85" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -7935,12 +8115,12 @@
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>杀伐诀</t>
+          <t>寸劲篇</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>被动，攻击+12%</t>
+          <t>被动，攻击+12%；开战，自身受击权重+6（寸劲贴身）</t>
         </is>
       </c>
       <c r="D86" s="0" t="n">
@@ -8011,6 +8191,21 @@
       </c>
       <c r="AA86" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB86" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC86" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD86" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE86" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -8019,12 +8214,12 @@
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>刚猛功</t>
+          <t>运掌心法</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>被动，攻击+12%</t>
+          <t>被动，攻击+12%；开战，自身护盾=气血上限8%</t>
         </is>
       </c>
       <c r="D87" s="0" t="n">
@@ -8095,6 +8290,21 @@
       </c>
       <c r="AA87" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB87" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC87" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD87" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE87" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF87" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -8103,12 +8313,12 @@
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>攻坚篇</t>
+          <t>下盘功</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>被动，攻击+18%</t>
+          <t>被动，攻击+18%；开战，自身速度+10%</t>
         </is>
       </c>
       <c r="D88" s="0" t="n">
@@ -8179,6 +8389,21 @@
       </c>
       <c r="AA88" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB88" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC88" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD88" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE88" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF88" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -8187,12 +8412,12 @@
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>锐意诀</t>
+          <t>缠丝劲</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>被动，攻击+18%</t>
+          <t>被动，攻击+18%；被动，护盾保持率+10 点</t>
         </is>
       </c>
       <c r="D89" s="0" t="n">
@@ -8263,6 +8488,21 @@
       </c>
       <c r="AA89" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB89" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC89" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD89" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE89" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF89" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -8271,7 +8511,7 @@
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>伐髓经</t>
+          <t>藏机篇</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
@@ -8355,7 +8595,7 @@
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>轻身诀</t>
+          <t>踏虚篇</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
@@ -8439,12 +8679,12 @@
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>疾风篇</t>
+          <t>岐黄录</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>被动，速度+7%</t>
+          <t>被动，速度+7%；开战，己方全体治疗=气血上限5%</t>
         </is>
       </c>
       <c r="D92" s="0" t="n">
@@ -8515,6 +8755,21 @@
       </c>
       <c r="AA92" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="AB92" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC92" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD92" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -8523,12 +8778,12 @@
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>迅影功</t>
+          <t>百蛊诀</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>被动，速度+10%</t>
+          <t>被动，速度+10%；开战，自身攻击+6%</t>
         </is>
       </c>
       <c r="D93" s="0" t="n">
@@ -8599,6 +8854,21 @@
       </c>
       <c r="AA93" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB93" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC93" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD93" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE93" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF93" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -8607,7 +8877,7 @@
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>快步诀</t>
+          <t>观星诀</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
@@ -8691,12 +8961,12 @@
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>踏云篇</t>
+          <t>禅心不动</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>被动，速度+15%</t>
+          <t>被动，速度+15%；被动，护盾保持率+10 点</t>
         </is>
       </c>
       <c r="D95" s="0" t="n">
@@ -8767,6 +9037,21 @@
       </c>
       <c r="AA95" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB95" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC95" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD95" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE95" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF95" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -8775,7 +9060,7 @@
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>不动明王</t>
+          <t>兽血篇</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
@@ -8859,12 +9144,12 @@
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>静心诀</t>
+          <t>守拙剑意</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>被动，受击权重+7</t>
+          <t>被动，受击权重+7；开战，自身护盾保持率+8点（整场）</t>
         </is>
       </c>
       <c r="D97" s="0" t="n">
@@ -8935,6 +9220,21 @@
       </c>
       <c r="AA97" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="AB97" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC97" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD97" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8943,12 +9243,12 @@
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>藏锋篇</t>
+          <t>锋锐录</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>被动，受击权重+10</t>
+          <t>被动，受击权重+10；开战，自身攻击+8%</t>
         </is>
       </c>
       <c r="D98" s="0" t="n">
@@ -9019,6 +9319,21 @@
       </c>
       <c r="AA98" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB98" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC98" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD98" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE98" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF98" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -9027,12 +9342,12 @@
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>敛息功</t>
+          <t>拳理通微</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>被动，受击权重+14</t>
+          <t>被动，受击权重+14；开战，自身攻击+10%</t>
         </is>
       </c>
       <c r="D99" s="0" t="n">
@@ -9103,6 +9418,21 @@
       </c>
       <c r="AA99" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB99" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC99" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD99" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE99" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -9111,7 +9441,7 @@
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>守拙篇</t>
+          <t>绵掌篇</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
@@ -9195,7 +9525,7 @@
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>固盾诀</t>
+          <t>桩功篇</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
@@ -9279,12 +9609,12 @@
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>凝甲功</t>
+          <t>长鞭心法</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>被动，护盾保持率+15 点</t>
+          <t>被动，护盾保持率+15 点；开战，自身护盾=气血上限8%</t>
         </is>
       </c>
       <c r="D102" s="0" t="n">
@@ -9355,6 +9685,21 @@
       </c>
       <c r="AA102" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB102" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD102" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE102" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF102" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -9363,12 +9708,12 @@
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>厚壁篇</t>
+          <t>手眼通明</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>被动，护盾保持率+20 点</t>
+          <t>被动，护盾保持率+20 点；开战，自身攻击+8%</t>
         </is>
       </c>
       <c r="D103" s="0" t="n">
@@ -9439,6 +9784,21 @@
       </c>
       <c r="AA103" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB103" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC103" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD103" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE103" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF103" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -9447,7 +9807,7 @@
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>铁衣功</t>
+          <t>敛息诀</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
@@ -9531,7 +9891,7 @@
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>卸力篇</t>
+          <t>悬壶篇</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
@@ -9615,12 +9975,12 @@
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>化劲诀</t>
+          <t>炼毒录</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>被动，受击伤害-12%</t>
+          <t>被动，受击伤害-12%；开战，自身护盾保持率+8 点</t>
         </is>
       </c>
       <c r="D106" s="0" t="n">
@@ -9691,6 +10051,21 @@
       </c>
       <c r="AA106" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB106" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC106" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD106" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE106" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF106" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -9699,7 +10074,7 @@
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>起手势</t>
+          <t>衍数篇</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
@@ -9783,12 +10158,12 @@
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>先发篇</t>
+          <t>息尘篇</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>开战，己方次数型武学当前计数+1</t>
+          <t>开战，己方次数型武学当前计数+1；另：己方全体护盾=气血上限5%</t>
         </is>
       </c>
       <c r="D108" s="0" t="n">
@@ -9859,6 +10234,21 @@
       </c>
       <c r="AA108" s="0" t="n">
         <v>1</v>
+      </c>
+      <c r="AB108" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC108" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD108" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -9867,7 +10257,7 @@
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>蓄势诀</t>
+          <t>虎踞功</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
@@ -9951,7 +10341,7 @@
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>临阵篇</t>
+          <t>无锋篇</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
@@ -10035,12 +10425,12 @@
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>抢先手</t>
+          <t>刀意浑圆</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>开战，己方次数型武学当前计数+2</t>
+          <t>开战，己方次数型武学当前计数+2；开战，自身攻击+8%</t>
         </is>
       </c>
       <c r="D111" s="0" t="n">
@@ -10111,6 +10501,21 @@
       </c>
       <c r="AA111" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB111" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC111" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD111" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE111" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF111" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -10119,12 +10524,12 @@
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>锐气诀</t>
+          <t>铁桥诀</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>开战，己方次数型武学当前计数+2</t>
+          <t>开战，己方次数型武学当前计数+2；开战，自身护盾=气血上限8%</t>
         </is>
       </c>
       <c r="D112" s="0" t="n">
@@ -10195,6 +10600,21 @@
       </c>
       <c r="AA112" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB112" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC112" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD112" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE112" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -10203,12 +10623,12 @@
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>战机篇</t>
+          <t>掌意化虚</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>开战，己方次数型武学当前计数+3</t>
+          <t>开战，己方次数型武学当前计数+3；开战，自身护盾=气血上限12%</t>
         </is>
       </c>
       <c r="D113" s="0" t="n">
@@ -10279,6 +10699,21 @@
       </c>
       <c r="AA113" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB113" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC113" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD113" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE113" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF113" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -10287,12 +10722,12 @@
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>疾起功</t>
+          <t>腿法十要</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>开战，己方次数型武学当前计数+3</t>
+          <t>开战，己方次数型武学当前计数+3；开战，自身速度+12%</t>
         </is>
       </c>
       <c r="D114" s="0" t="n">
@@ -10363,6 +10798,21 @@
       </c>
       <c r="AA114" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB114" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC114" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD114" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE114" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF114" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -10371,7 +10821,7 @@
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>护身咒</t>
+          <t>柔丝诀</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
@@ -10455,7 +10905,7 @@
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>开山甲</t>
+          <t>袖中机</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
@@ -10539,12 +10989,12 @@
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>金刚罩</t>
+          <t>游身八法</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>开战，己方全体护盾=气血上限18%</t>
+          <t>开战，己方全体护盾=气血上限18%；开战，另附全体治疗=气血上限10%</t>
         </is>
       </c>
       <c r="D117" s="0" t="n">
@@ -10615,6 +11065,21 @@
       </c>
       <c r="AA117" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB117" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC117" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD117" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE117" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF117" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -10623,12 +11088,12 @@
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>护体篇</t>
+          <t>养元经</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>开战，己方全体护盾=气血上限26%</t>
+          <t>开战，己方全体护盾=气血上限26%；开战，另附治疗=气血上限15%</t>
         </is>
       </c>
       <c r="D118" s="0" t="n">
@@ -10699,6 +11164,21 @@
       </c>
       <c r="AA118" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB118" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC118" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD118" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE118" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF118" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -10707,12 +11187,12 @@
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>回春篇</t>
+          <t>毒经疏</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>开战，己方全体持续治疗=气血上限1.0%/跳(2s)</t>
+          <t>开战，己方全体HoT 2层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D119" s="0" t="n">
@@ -10740,10 +11220,10 @@
         <v>20</v>
       </c>
       <c r="L119" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M119" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N119" s="0" t="n">
         <v>5</v>
@@ -10791,12 +11271,12 @@
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>续命诀</t>
+          <t>奇门要略</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>开战，己方全体持续治疗=气血上限1.5%/跳(2s)</t>
+          <t>开战，己方全体HoT 4层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D120" s="0" t="n">
@@ -10824,10 +11304,10 @@
         <v>20</v>
       </c>
       <c r="L120" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M120" s="0" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="N120" s="0" t="n">
         <v>5</v>
@@ -10876,12 +11356,12 @@
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>养生功</t>
+          <t>舍身经</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>开战，己方全体持续治疗=气血上限2.0%/跳(2s)</t>
+          <t>开战，己方全体HoT 6层（每层1点/2s）；开战，另附全体护盾=气血上限12%</t>
         </is>
       </c>
       <c r="D121" s="0" t="n">
@@ -10909,10 +11389,10 @@
         <v>20</v>
       </c>
       <c r="L121" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M121" s="0" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N121" s="0" t="n">
         <v>5</v>
@@ -10952,6 +11432,21 @@
       </c>
       <c r="AA121" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB121" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC121" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD121" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -10960,7 +11455,7 @@
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>唤灵诀</t>
+          <t>驯兽诀</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
@@ -11049,7 +11544,7 @@
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>引兽篇</t>
+          <t>剑心通明</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
@@ -11138,12 +11633,12 @@
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>召影功</t>
+          <t>重楼刀意</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>开战，召唤一只随从</t>
+          <t>开战，召唤一只随从；开战，自身攻击+10%</t>
         </is>
       </c>
       <c r="D124" s="0" t="n">
@@ -11219,6 +11714,21 @@
       </c>
       <c r="AA124" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB124" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC124" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD124" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE124" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF124" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -11227,7 +11737,7 @@
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>白虹劲</t>
+          <t>断腕夺势</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
@@ -11311,12 +11821,12 @@
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>晓风式</t>
+          <t>抚伤掌</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，持续治疗=气血上限4.4%/跳(2s)</t>
+          <t>行动每4次，HoT 6层（每层1点/2s）；另：护盾=气血上限5%</t>
         </is>
       </c>
       <c r="D126" s="0" t="n">
@@ -11344,10 +11854,10 @@
         <v>20</v>
       </c>
       <c r="L126" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M126" s="0" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="N126" s="0" t="n">
         <v>0</v>
@@ -11387,6 +11897,21 @@
       </c>
       <c r="AA126" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB126" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC126" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD126" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE126" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF126" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -11395,12 +11920,12 @@
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>游龙踢</t>
+          <t>碎星腿</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>行动15%，3.38×伤害</t>
+          <t>行动15%，3.38×伤害（外功）；另：每6次，0.56×第二段（外功，连踢）</t>
         </is>
       </c>
       <c r="D127" s="0" t="n">
@@ -11471,6 +11996,21 @@
       </c>
       <c r="AA127" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB127" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC127" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD127" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="AE127" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF127" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -11479,12 +12019,12 @@
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>破浪缠</t>
+          <t>裂空鞭</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>受击每6次，1.2×反伤给攻击者（外功）</t>
+          <t>受击每6次，1.2×反伤给攻击者（外功）；另：攻击者SPD−10%(10s)</t>
         </is>
       </c>
       <c r="D128" s="0" t="n">
@@ -11555,6 +12095,21 @@
       </c>
       <c r="AA128" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB128" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC128" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD128" s="0" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AE128" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF128" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -11563,12 +12118,12 @@
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>听雨镖</t>
+          <t>无相·夺魂针</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>受击每7次，1.75×反伤给攻击者（外功）</t>
+          <t>受击每6次，1.63×反伤给攻击者（外功）；另：给攻击者叠毒8层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D129" s="0" t="n">
@@ -11581,7 +12136,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H129" s="0" t="n">
         <v>0</v>
@@ -11599,7 +12154,7 @@
         <v>1</v>
       </c>
       <c r="M129" s="0" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="N129" s="0" t="n">
         <v>6</v>
@@ -11639,6 +12194,21 @@
       </c>
       <c r="AA129" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB129" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC129" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD129" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE129" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF129" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -11647,12 +12217,12 @@
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>拂柳身法</t>
+          <t>惊鸿照影</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，7.56×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：行动每2次，0.8×伤害（外功）</t>
         </is>
       </c>
       <c r="D130" s="0" t="n">
@@ -11665,7 +12235,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H130" s="0" t="n">
         <v>0</v>
@@ -11683,7 +12253,7 @@
         <v>1</v>
       </c>
       <c r="M130" s="0" t="n">
-        <v>756</v>
+        <v>588</v>
       </c>
       <c r="N130" s="0" t="n">
         <v>1</v>
@@ -11723,6 +12293,21 @@
       </c>
       <c r="AA130" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB130" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC130" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD130" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE130" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF130" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -11731,12 +12316,12 @@
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>寒鸦术</t>
+          <t>回春手</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，持续治疗=气血上限1.5%/跳(2s)</t>
+          <t>行动每3次，HoT 2层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D131" s="0" t="n">
@@ -11764,10 +12349,10 @@
         <v>20</v>
       </c>
       <c r="L131" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M131" s="0" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N131" s="0" t="n">
         <v>0</v>
@@ -11815,12 +12400,12 @@
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>御风散</t>
+          <t>蛇涎散</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>受击每10次，给攻击者叠毒1层（层数不衰减，上限5）</t>
+          <t>受击每6次，给攻击者叠毒2层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D132" s="0" t="n">
@@ -11833,7 +12418,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H132" s="0" t="n">
         <v>0</v>
@@ -11851,7 +12436,7 @@
         <v>3</v>
       </c>
       <c r="M132" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N132" s="0" t="n">
         <v>6</v>
@@ -11899,12 +12484,12 @@
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>大寒术</t>
+          <t>五行移位</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，1.91×内功</t>
+          <t>行动每5次，伤害=当前护盾×50%（内功，不消耗护盾，需有护盾）</t>
         </is>
       </c>
       <c r="D133" s="0" t="n">
@@ -11929,13 +12514,13 @@
         <v>2</v>
       </c>
       <c r="K133" s="0" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L133" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M133" s="0" t="n">
-        <v>191</v>
+        <v>50</v>
       </c>
       <c r="N133" s="0" t="n">
         <v>1</v>
@@ -11983,7 +12568,7 @@
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>大雪禅</t>
+          <t>枯禅录</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
@@ -12067,12 +12652,12 @@
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>残阳爪</t>
+          <t>青蛇缚身</t>
         </is>
       </c>
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，目标ATK−15%(10s)</t>
+          <t>行动每6次，目标ATK−15%(10s)</t>
         </is>
       </c>
       <c r="D135" s="0" t="n">
@@ -12085,7 +12670,7 @@
         <v>1</v>
       </c>
       <c r="G135" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H135" s="0" t="n">
         <v>0</v>
@@ -12151,12 +12736,12 @@
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>飞星诀</t>
+          <t>百炼霜锋</t>
         </is>
       </c>
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，4.68×伤害</t>
+          <t>行动每6次，3.64×伤害（外功）；另：行动每4次，0.8×伤害（外功）</t>
         </is>
       </c>
       <c r="D136" s="0" t="n">
@@ -12169,7 +12754,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H136" s="0" t="n">
         <v>0</v>
@@ -12187,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="M136" s="0" t="n">
-        <v>468</v>
+        <v>364</v>
       </c>
       <c r="N136" s="0" t="n">
         <v>1</v>
@@ -12227,6 +12812,21 @@
       </c>
       <c r="AA136" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB136" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC136" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD136" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE136" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF136" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -12235,12 +12835,12 @@
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>流火法</t>
+          <t>铁骑突出</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>行动35%，反弹累计受击伤害46%</t>
+          <t>行动35%，反弹累计受击伤害46%（内功）；另：每3次，护盾=气血上限5%（先攒后弹）</t>
         </is>
       </c>
       <c r="D137" s="0" t="n">
@@ -12311,6 +12911,21 @@
       </c>
       <c r="AA137" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB137" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC137" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD137" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE137" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF137" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -12319,12 +12934,12 @@
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>玄冰手</t>
+          <t>百步崩山</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>受击每6次，1.2×反伤给攻击者（外功）</t>
+          <t>受击每6次，1.2×反伤给攻击者（外功）；另：自身攻击叠乘+2%/次</t>
         </is>
       </c>
       <c r="D138" s="0" t="n">
@@ -12395,6 +13010,21 @@
       </c>
       <c r="AA138" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB138" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC138" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF138" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -12403,12 +13033,12 @@
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>孤烟功</t>
+          <t>无相·落星掌</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，4.73×内功</t>
+          <t>行动每5次，4.73×伤害（内功）；另：目标ATK−18%(10s)</t>
         </is>
       </c>
       <c r="D139" s="0" t="n">
@@ -12479,6 +13109,21 @@
       </c>
       <c r="AA139" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB139" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC139" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD139" s="0" t="n">
+        <v>-18</v>
+      </c>
+      <c r="AE139" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF139" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -12487,12 +13132,12 @@
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>夺魄步</t>
+          <t>绝腿·山崩</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，5.88×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：行动每2次，0.7×伤害（外功，连踢）</t>
         </is>
       </c>
       <c r="D140" s="0" t="n">
@@ -12563,6 +13208,21 @@
       </c>
       <c r="AA140" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB140" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC140" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD140" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE140" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF140" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -12571,7 +13231,7 @@
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>沉渊索</t>
+          <t>缠丝鞭</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
@@ -12655,12 +13315,12 @@
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>望月手</t>
+          <t>封喉针</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，沉默5s</t>
+          <t>行动每6次，引爆目标毒层（每层0.47×攻击，内功，引爆即清空）；另：附带沉默5s（每场1次）</t>
         </is>
       </c>
       <c r="D142" s="0" t="n">
@@ -12673,63 +13333,78 @@
         <v>1</v>
       </c>
       <c r="G142" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K142" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="L142" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" s="0" t="n">
+        <v>47</v>
+      </c>
+      <c r="N142" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O142" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="S142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="W142" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB142" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="H142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J142" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K142" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="L142" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O142" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="P142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="S142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="W142" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="X142" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y142" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z142" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA142" s="0" t="n">
+      <c r="AC142" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF142" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12739,7 +13414,7 @@
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>惊鸿影</t>
+          <t>缠风绕柳</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
@@ -12823,7 +13498,7 @@
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>断桥经</t>
+          <t>续命汤</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
@@ -12907,12 +13582,12 @@
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>惊蛰功</t>
+          <t>断肠草</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>受击每9次，给攻击者叠毒1层（层数不衰减，上限5）</t>
+          <t>受击每6次，给攻击者叠毒4层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D145" s="0" t="n">
@@ -12925,7 +13600,7 @@
         <v>1</v>
       </c>
       <c r="G145" s="0" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H145" s="0" t="n">
         <v>0</v>
@@ -12943,7 +13618,7 @@
         <v>3</v>
       </c>
       <c r="M145" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N145" s="0" t="n">
         <v>6</v>
@@ -12991,12 +13666,12 @@
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>清明机</t>
+          <t>傀儡引</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，召唤随从</t>
+          <t>行动每6次，召唤随从；另：0.9×伤害（外功）</t>
         </is>
       </c>
       <c r="D146" s="0" t="n">
@@ -13072,6 +13747,21 @@
       </c>
       <c r="AA146" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB146" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC146" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD146" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE146" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF146" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -13080,12 +13770,12 @@
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>裂云印</t>
+          <t>甘露咒</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>行动25%，护盾=气血上限16%</t>
+          <t>行动25%，护盾=气血上限16%；另：每4次，治疗=气血上限6%</t>
         </is>
       </c>
       <c r="D147" s="0" t="n">
@@ -13156,6 +13846,21 @@
       </c>
       <c r="AA147" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB147" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC147" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD147" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE147" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF147" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -13164,12 +13869,12 @@
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>飞星形</t>
+          <t>驱狼逐鹿</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，召唤随从</t>
+          <t>行动每6次，召唤随从；另：目标W+8(10s)</t>
         </is>
       </c>
       <c r="D148" s="0" t="n">
@@ -13182,7 +13887,7 @@
         <v>1</v>
       </c>
       <c r="G148" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H148" s="0" t="n">
         <v>0</v>
@@ -13245,6 +13950,21 @@
       </c>
       <c r="AA148" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB148" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC148" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD148" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE148" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF148" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -13253,12 +13973,12 @@
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>落雁剑</t>
+          <t>明锋喝阵</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，目标W+19(10s)</t>
+          <t>行动每3次，目标W+19(10s)；另：行动每6次，斩杀=目标已损气血20%（外功，每场1次）</t>
         </is>
       </c>
       <c r="D149" s="0" t="n">
@@ -13329,6 +14049,21 @@
       </c>
       <c r="AA149" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB149" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC149" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD149" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE149" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF149" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -13337,12 +14072,12 @@
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>碎玉刀</t>
+          <t>千军辟易</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，消耗全部护盾转化为等量内功伤害</t>
+          <t>行动每4次，消耗全部护盾转化为等量内功伤害；另：1.2×伤害（外功，爆盾之外再补一刀）</t>
         </is>
       </c>
       <c r="D150" s="0" t="n">
@@ -13413,6 +14148,21 @@
       </c>
       <c r="AA150" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC150" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD150" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE150" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF150" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -13421,12 +14171,12 @@
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>赤霄拳</t>
+          <t>崩山拳</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，1.25×伤害</t>
+          <t>行动每5次，1.25×伤害（外功）</t>
         </is>
       </c>
       <c r="D151" s="0" t="n">
@@ -13505,12 +14255,12 @@
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>长空掌</t>
+          <t>推山掌</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，1.26×内功</t>
+          <t>行动每6次，1.26×伤害（内功）</t>
         </is>
       </c>
       <c r="D152" s="0" t="n">
@@ -13589,7 +14339,7 @@
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>刺骨腿</t>
+          <t>绊马腿</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
@@ -13673,7 +14423,7 @@
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>焚天鞭</t>
+          <t>回风鞭</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
@@ -13757,12 +14507,12 @@
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>疏影针</t>
+          <t>柳叶镖</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.70×伤害</t>
+          <t>行动每4次，叠毒4层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D155" s="0" t="n">
@@ -13775,7 +14525,7 @@
         <v>1</v>
       </c>
       <c r="G155" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H155" s="0" t="n">
         <v>0</v>
@@ -13784,16 +14534,16 @@
         <v>0</v>
       </c>
       <c r="J155" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K155" s="0" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L155" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M155" s="0" t="n">
-        <v>170</v>
+        <v>4</v>
       </c>
       <c r="N155" s="0" t="n">
         <v>1</v>
@@ -13841,19 +14591,19 @@
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>振衣步</t>
+          <t>踏雪无痕</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，完全闪避该次攻击</t>
+          <t>受击每4次，完全闪避该次攻击；另：0.6×伤害（外功，闪后反击）</t>
         </is>
       </c>
       <c r="D156" s="0" t="n">
         <v>8</v>
       </c>
       <c r="E156" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="0" t="n">
         <v>1</v>
@@ -13917,6 +14667,21 @@
       </c>
       <c r="AA156" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB156" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC156" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD156" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE156" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF156" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -13925,12 +14690,12 @@
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>穿林诀</t>
+          <t>五石散</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>行动15%，护盾=气血上限20%</t>
+          <t>行动15%，护盾=气血上限20%；另：每6次，治疗=气血上限7%</t>
         </is>
       </c>
       <c r="D157" s="0" t="n">
@@ -14001,6 +14766,21 @@
       </c>
       <c r="AA157" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB157" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC157" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD157" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE157" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF157" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -14009,12 +14789,12 @@
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>白露掌</t>
+          <t>化力香</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，目标ATK−18%(10s)</t>
+          <t>行动每6次，目标ATK−18%(10s)；另：同时叠毒6层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D158" s="0" t="n">
@@ -14085,6 +14865,21 @@
       </c>
       <c r="AA158" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB158" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC158" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD158" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE158" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF158" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -14093,12 +14888,12 @@
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>谷雨阵</t>
+          <t>聚煞阵</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，目标W+19(10s)</t>
+          <t>行动每6次，目标W+19(10s)；另：护盾=气血上限9%</t>
         </is>
       </c>
       <c r="D159" s="0" t="n">
@@ -14111,7 +14906,7 @@
         <v>1</v>
       </c>
       <c r="G159" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H159" s="0" t="n">
         <v>0</v>
@@ -14169,6 +14964,21 @@
       </c>
       <c r="AA159" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB159" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC159" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD159" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE159" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF159" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -14177,12 +14987,12 @@
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>断岳功</t>
+          <t>无相·碎妄</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>受击每7次，1.75×反伤给攻击者（外功）</t>
+          <t>受击每6次，1.63×反伤给攻击者（外功）；另：护盾=气血上限7%</t>
         </is>
       </c>
       <c r="D160" s="0" t="n">
@@ -14195,7 +15005,7 @@
         <v>1</v>
       </c>
       <c r="G160" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H160" s="0" t="n">
         <v>0</v>
@@ -14213,7 +15023,7 @@
         <v>1</v>
       </c>
       <c r="M160" s="0" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="N160" s="0" t="n">
         <v>6</v>
@@ -14253,6 +15063,21 @@
       </c>
       <c r="AA160" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB160" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC160" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD160" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE160" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF160" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -14261,7 +15086,7 @@
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>落雁诀</t>
+          <t>唤鹰击空</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
@@ -14350,7 +15175,7 @@
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>惊雷斩</t>
+          <t>三寸青锋</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
@@ -14434,12 +15259,12 @@
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>沉沙斩</t>
+          <t>拖刀断水</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，2.12×伤害</t>
+          <t>行动每6次，2.12×伤害（外功），打敌方血最少</t>
         </is>
       </c>
       <c r="D163" s="0" t="n">
@@ -14473,7 +15298,7 @@
         <v>212</v>
       </c>
       <c r="N163" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O163" s="0" t="b">
         <v>0</v>
@@ -14518,12 +15343,12 @@
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>苍梧劲</t>
+          <t>裂石拳</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>行动20%，反弹累计受击伤害40%</t>
+          <t>行动20%，反弹累计受击伤害40%（内功）</t>
         </is>
       </c>
       <c r="D164" s="0" t="n">
@@ -14602,12 +15427,12 @@
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>踏雪式</t>
+          <t>卸甲掌</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，目标ATK−15%(10s)</t>
+          <t>行动每6次，目标ATK−15%(10s)</t>
         </is>
       </c>
       <c r="D165" s="0" t="n">
@@ -14620,7 +15445,7 @@
         <v>1</v>
       </c>
       <c r="G165" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H165" s="0" t="n">
         <v>0</v>
@@ -14686,12 +15511,12 @@
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>锁喉踢</t>
+          <t>五步穿心</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，4.68×伤害</t>
+          <t>行动每6次，3.64×伤害（外功）；另：目标W+8(10s)（穿心后露破绽）</t>
         </is>
       </c>
       <c r="D166" s="0" t="n">
@@ -14704,7 +15529,7 @@
         <v>1</v>
       </c>
       <c r="G166" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H166" s="0" t="n">
         <v>0</v>
@@ -14722,7 +15547,7 @@
         <v>1</v>
       </c>
       <c r="M166" s="0" t="n">
-        <v>468</v>
+        <v>364</v>
       </c>
       <c r="N166" s="0" t="n">
         <v>1</v>
@@ -14762,6 +15587,21 @@
       </c>
       <c r="AA166" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB166" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC166" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD166" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE166" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF166" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -14770,12 +15610,12 @@
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>碎星缠</t>
+          <t>牵锋诀</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>行动35%，目标W+14(10s)</t>
+          <t>行动35%，目标W+14(10s)；另：每3次，0.8×伤害（外功，牵住再打）</t>
         </is>
       </c>
       <c r="D167" s="0" t="n">
@@ -14846,6 +15686,21 @@
       </c>
       <c r="AA167" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB167" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC167" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD167" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE167" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF167" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -14854,12 +15709,12 @@
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>暗香镖</t>
+          <t>蚀心砂</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>受击每6次，给攻击者叠毒1层（层数不衰减，上限5）</t>
+          <t>受击每6次，给攻击者叠毒6层（每层1点/秒，无视护盾，不衰减、无上限）；另：0.6×伤害（外功）</t>
         </is>
       </c>
       <c r="D168" s="0" t="n">
@@ -14881,7 +15736,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K168" s="0" t="n">
         <v>8</v>
@@ -14890,7 +15745,7 @@
         <v>3</v>
       </c>
       <c r="M168" s="0" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N168" s="0" t="n">
         <v>6</v>
@@ -14930,6 +15785,21 @@
       </c>
       <c r="AA168" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB168" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC168" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD168" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE168" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF168" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -14938,19 +15808,19 @@
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>裂帛身法</t>
+          <t>无相·残影</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，完全闪避该次攻击</t>
+          <t>受击每5次，完全闪避该次攻击；另：攻击者SPD−20%(10s)（闪身反制）</t>
         </is>
       </c>
       <c r="D169" s="0" t="n">
         <v>8</v>
       </c>
       <c r="E169" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169" s="0" t="n">
         <v>1</v>
@@ -15014,6 +15884,21 @@
       </c>
       <c r="AA169" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB169" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC169" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD169" s="0" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AE169" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF169" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -15022,12 +15907,12 @@
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>涉川术</t>
+          <t>无相·续灯</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，持续治疗=气血上限8.8%/跳(2s)</t>
+          <t>行动每6次，HoT 8层（每层1点/2s）；另：护盾=气血上限6%</t>
         </is>
       </c>
       <c r="D170" s="0" t="n">
@@ -15055,10 +15940,10 @@
         <v>20</v>
       </c>
       <c r="L170" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M170" s="0" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="N170" s="0" t="n">
         <v>0</v>
@@ -15098,6 +15983,21 @@
       </c>
       <c r="AA170" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB170" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC170" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD170" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE170" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF170" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -15106,12 +16006,12 @@
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>霜降散</t>
+          <t>鹤顶红</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，叠毒1层(每秒0.2×，不衰减，上限5)</t>
+          <t>行动每6次，叠毒2层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D171" s="0" t="n">
@@ -15124,7 +16024,7 @@
         <v>1</v>
       </c>
       <c r="G171" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H171" s="0" t="n">
         <v>0</v>
@@ -15139,10 +16039,10 @@
         <v>8</v>
       </c>
       <c r="L171" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M171" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N171" s="0" t="n">
         <v>1</v>
@@ -15190,12 +16090,12 @@
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>芒种术</t>
+          <t>引雷符</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，消耗全部护盾转化为等量内功伤害</t>
+          <t>行动每6次，消耗全部护盾转化为等量内功伤害</t>
         </is>
       </c>
       <c r="D172" s="0" t="n">
@@ -15208,7 +16108,7 @@
         <v>1</v>
       </c>
       <c r="G172" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H172" s="0" t="n">
         <v>0</v>
@@ -15274,7 +16174,7 @@
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>寒江禅</t>
+          <t>渡世灯</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
@@ -15358,12 +16258,12 @@
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>惊雷爪</t>
+          <t>玄豹扑食</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>行动10%，2.46×伤害</t>
+          <t>行动10%，2.46×伤害（外功）</t>
         </is>
       </c>
       <c r="D174" s="0" t="n">
@@ -15442,7 +16342,7 @@
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>霜刃式</t>
+          <t>落雁回风</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
@@ -15526,12 +16426,12 @@
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>枯木法</t>
+          <t>霜刃试锋</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，3.64×伤害</t>
+          <t>行动每6次，3.64×伤害（外功）；另：目标ATK−12%(10s)</t>
         </is>
       </c>
       <c r="D176" s="0" t="n">
@@ -15602,6 +16502,21 @@
       </c>
       <c r="AA176" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB176" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC176" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD176" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE176" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF176" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -15610,12 +16525,12 @@
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>夜雨手</t>
+          <t>万钧落</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>行动25%，2.73×伤害</t>
+          <t>行动25%，2.73×伤害（外功）；另：每4次，目标ATK−12%(10s)</t>
         </is>
       </c>
       <c r="D177" s="0" t="n">
@@ -15686,6 +16601,21 @@
       </c>
       <c r="AA177" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB177" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC177" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD177" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE177" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF177" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -15694,12 +16624,12 @@
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>回风功</t>
+          <t>迟脉掌</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，目标SPD−18%(10s)</t>
+          <t>行动每6次，目标SPD−18%(10s)；另：0.62×伤害（外功）</t>
         </is>
       </c>
       <c r="D178" s="0" t="n">
@@ -15712,7 +16642,7 @@
         <v>1</v>
       </c>
       <c r="G178" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H178" s="0" t="n">
         <v>0</v>
@@ -15770,6 +16700,21 @@
       </c>
       <c r="AA178" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC178" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD178" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="AE178" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF178" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -15778,12 +16723,12 @@
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>卷云步</t>
+          <t>引锋踏阵</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，目标W+19(10s)</t>
+          <t>行动每3次，目标W+19(10s)；另：目标SPD−15%(10s)（绊住再集火）</t>
         </is>
       </c>
       <c r="D179" s="0" t="n">
@@ -15854,6 +16799,21 @@
       </c>
       <c r="AA179" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB179" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD179" s="0" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AE179" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF179" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -15862,12 +16822,12 @@
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>吞山索</t>
+          <t>封喉鞭</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，沉默5s</t>
+          <t>行动每4次，沉默5s；另：同时叠毒8层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D180" s="0" t="n">
@@ -15938,6 +16898,21 @@
       </c>
       <c r="AA180" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB180" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC180" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD180" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE180" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF180" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -15946,12 +16921,12 @@
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>削竹手</t>
+          <t>飞蝗石</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，1.25×伤害</t>
+          <t>行动每6次，叠毒2层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D181" s="0" t="n">
@@ -15964,7 +16939,7 @@
         <v>1</v>
       </c>
       <c r="G181" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H181" s="0" t="n">
         <v>0</v>
@@ -15973,16 +16948,16 @@
         <v>0</v>
       </c>
       <c r="J181" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181" s="0" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L181" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M181" s="0" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="N181" s="0" t="n">
         <v>1</v>
@@ -16030,7 +17005,7 @@
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>落英影</t>
+          <t>引风招敌</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
@@ -16114,7 +17089,7 @@
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>踏浪经</t>
+          <t>露华方</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
@@ -16198,12 +17173,12 @@
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>小寒功</t>
+          <t>焚风砂</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>行动30%，灼烧(每秒0.25×，每跳衰减10%%，10s)</t>
+          <t>行动30%，灼烧6层（每层1点/秒，被护盾吸收，10s）</t>
         </is>
       </c>
       <c r="D184" s="0" t="n">
@@ -16231,10 +17206,10 @@
         <v>9</v>
       </c>
       <c r="L184" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M184" s="0" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N184" s="0" t="n">
         <v>1</v>
@@ -16282,12 +17257,12 @@
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>处暑机</t>
+          <t>六丁符</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.53×内功</t>
+          <t>行动每3次，伤害=当前护盾×40%（内功，不消耗护盾，需有护盾）</t>
         </is>
       </c>
       <c r="D185" s="0" t="n">
@@ -16312,13 +17287,13 @@
         <v>2</v>
       </c>
       <c r="K185" s="0" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L185" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M185" s="0" t="n">
-        <v>153</v>
+        <v>40</v>
       </c>
       <c r="N185" s="0" t="n">
         <v>1</v>
@@ -16366,12 +17341,12 @@
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>孤鸿印</t>
+          <t>伏魔印</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，2.91×伤害</t>
+          <t>行动每4次，2.91×伤害（外功）；另：目标ATK−12%(10s)</t>
         </is>
       </c>
       <c r="D186" s="0" t="n">
@@ -16442,6 +17417,21 @@
       </c>
       <c r="AA186" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB186" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC186" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD186" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE186" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF186" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -16450,12 +17440,12 @@
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>霜刃形</t>
+          <t>狼嗥聚群</t>
         </is>
       </c>
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>行动15%，目标W+14(10s)</t>
+          <t>行动15%，目标W+14(10s)；另：每6次，目标ATK−12%(10s)</t>
         </is>
       </c>
       <c r="D187" s="0" t="n">
@@ -16526,6 +17516,21 @@
       </c>
       <c r="AA187" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB187" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC187" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD187" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE187" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF187" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -16534,12 +17539,12 @@
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>青锋诀</t>
+          <t>九曲回锋</t>
         </is>
       </c>
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，3.64×伤害</t>
+          <t>行动每6次，3.64×伤害（外功）；另：目标SPD−12%(10s)</t>
         </is>
       </c>
       <c r="D188" s="0" t="n">
@@ -16610,6 +17615,21 @@
       </c>
       <c r="AA188" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB188" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC188" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD188" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE188" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF188" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -16618,12 +17638,12 @@
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>白虹刀</t>
+          <t>十方无阻</t>
         </is>
       </c>
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，6.72×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：目标ATK−15%(10s)</t>
         </is>
       </c>
       <c r="D189" s="0" t="n">
@@ -16636,7 +17656,7 @@
         <v>1</v>
       </c>
       <c r="G189" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H189" s="0" t="n">
         <v>0</v>
@@ -16654,7 +17674,7 @@
         <v>1</v>
       </c>
       <c r="M189" s="0" t="n">
-        <v>672</v>
+        <v>588</v>
       </c>
       <c r="N189" s="0" t="n">
         <v>1</v>
@@ -16694,6 +17714,21 @@
       </c>
       <c r="AA189" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB189" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC189" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD189" s="0" t="n">
+        <v>-15</v>
+      </c>
+      <c r="AE189" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF189" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -16702,12 +17737,12 @@
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>晓风拳</t>
+          <t>无相·碎骨捶</t>
         </is>
       </c>
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，7.56×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：自身攻击叠乘+3%/次</t>
         </is>
       </c>
       <c r="D190" s="0" t="n">
@@ -16720,7 +17755,7 @@
         <v>1</v>
       </c>
       <c r="G190" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H190" s="0" t="n">
         <v>0</v>
@@ -16738,7 +17773,7 @@
         <v>1</v>
       </c>
       <c r="M190" s="0" t="n">
-        <v>756</v>
+        <v>588</v>
       </c>
       <c r="N190" s="0" t="n">
         <v>1</v>
@@ -16778,6 +17813,21 @@
       </c>
       <c r="AA190" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB190" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC190" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD190" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE190" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF190" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -16786,12 +17836,12 @@
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>游龙掌</t>
+          <t>拂云掌</t>
         </is>
       </c>
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，0.90×内功</t>
+          <t>行动每3次，0.90×伤害（内功）</t>
         </is>
       </c>
       <c r="D191" s="0" t="n">
@@ -16870,12 +17920,12 @@
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>破浪腿</t>
+          <t>撩风腿</t>
         </is>
       </c>
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，1.12×伤害</t>
+          <t>行动每4次，1.12×伤害（外功）</t>
         </is>
       </c>
       <c r="D192" s="0" t="n">
@@ -16954,7 +18004,7 @@
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>听雨鞭</t>
+          <t>绊索诀</t>
         </is>
       </c>
       <c r="C193" s="0" t="inlineStr">
@@ -17038,12 +18088,12 @@
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>拂柳针</t>
+          <t>烈焰砂</t>
         </is>
       </c>
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>行动20%，灼烧(每秒0.25×，每跳衰减10%%，10s)</t>
+          <t>行动每5次，引爆目标毒层（每层0.6×攻击，内功，引爆即清空）</t>
         </is>
       </c>
       <c r="D194" s="0" t="n">
@@ -17053,28 +18103,28 @@
         <v>1</v>
       </c>
       <c r="F194" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G194" s="0" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H194" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I194" s="0" t="n">
         <v>0</v>
       </c>
       <c r="J194" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K194" s="0" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L194" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M194" s="0" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N194" s="0" t="n">
         <v>1</v>
@@ -17114,6 +18164,15 @@
       </c>
       <c r="AA194" s="0" t="n">
         <v>2</v>
+      </c>
+      <c r="AB194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF194" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -17122,12 +18181,12 @@
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>寒鸦步</t>
+          <t>掠水行</t>
         </is>
       </c>
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，2.72×伤害</t>
+          <t>行动每6次，2.38×伤害（外功），打敌方血最少</t>
         </is>
       </c>
       <c r="D195" s="0" t="n">
@@ -17140,7 +18199,7 @@
         <v>1</v>
       </c>
       <c r="G195" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H195" s="0" t="n">
         <v>0</v>
@@ -17158,10 +18217,10 @@
         <v>1</v>
       </c>
       <c r="M195" s="0" t="n">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="N195" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O195" s="0" t="b">
         <v>0</v>
@@ -17206,12 +18265,12 @@
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>御风诀</t>
+          <t>九转还元</t>
         </is>
       </c>
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，护盾=气血上限28%</t>
+          <t>行动每6次，护盾=气血上限22%；另：HoT 6层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D196" s="0" t="n">
@@ -17224,7 +18283,7 @@
         <v>1</v>
       </c>
       <c r="G196" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H196" s="0" t="n">
         <v>0</v>
@@ -17242,7 +18301,7 @@
         <v>2</v>
       </c>
       <c r="M196" s="0" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N196" s="0" t="n">
         <v>0</v>
@@ -17282,6 +18341,21 @@
       </c>
       <c r="AA196" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB196" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC196" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD196" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE196" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF196" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -17290,12 +18364,12 @@
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>大寒掌</t>
+          <t>腐心散</t>
         </is>
       </c>
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>行动35%，叠毒1层(每秒0.2×，不衰减，上限5)</t>
+          <t>行动35%，叠毒6层（每层1点/秒，无视护盾，不衰减、无上限）；另：每3次，同时挂9层灼烧（每层1点/秒，被护盾吸收，10s）</t>
         </is>
       </c>
       <c r="D197" s="0" t="n">
@@ -17323,10 +18397,10 @@
         <v>8</v>
       </c>
       <c r="L197" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M197" s="0" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N197" s="0" t="n">
         <v>1</v>
@@ -17366,6 +18440,21 @@
       </c>
       <c r="AA197" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB197" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC197" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD197" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE197" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF197" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -17374,12 +18463,12 @@
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>大雪阵</t>
+          <t>噤声阵</t>
         </is>
       </c>
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，沉默5s</t>
+          <t>行动每4次，沉默5s；另：目标W+8(10s)</t>
         </is>
       </c>
       <c r="D198" s="0" t="n">
@@ -17450,6 +18539,21 @@
       </c>
       <c r="AA198" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB198" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC198" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD198" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE198" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF198" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -17458,12 +18562,12 @@
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>残阳功</t>
+          <t>绝禅·寂灭</t>
         </is>
       </c>
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，反弹累计受击伤害55%</t>
+          <t>行动每5次，伤害=当前护盾×90%（内功，不消耗护盾，需有护盾）；另：反弹累计受击伤害55%（内功）</t>
         </is>
       </c>
       <c r="D199" s="0" t="n">
@@ -17485,19 +18589,19 @@
         <v>0</v>
       </c>
       <c r="J199" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K199" s="0" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L199" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M199" s="0" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="N199" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O199" s="0" t="b">
         <v>0</v>
@@ -17534,6 +18638,21 @@
       </c>
       <c r="AA199" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB199" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC199" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD199" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE199" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF199" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -17542,12 +18661,12 @@
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>流火诀</t>
+          <t>绝兽·噬天</t>
         </is>
       </c>
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，5.88×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：目标W+14(10s)（撕开破绽）</t>
         </is>
       </c>
       <c r="D200" s="0" t="n">
@@ -17618,6 +18737,21 @@
       </c>
       <c r="AA200" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB200" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC200" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD200" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE200" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF200" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -17626,12 +18760,12 @@
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>流火剑</t>
+          <t>一式分光</t>
         </is>
       </c>
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，1.60×伤害</t>
+          <t>行动每3次，给目标挂1层破绽（每层：下一次受击受伤+40%）</t>
         </is>
       </c>
       <c r="D201" s="0" t="n">
@@ -17644,7 +18778,7 @@
         <v>1</v>
       </c>
       <c r="G201" s="0" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H201" s="0" t="n">
         <v>0</v>
@@ -17653,16 +18787,16 @@
         <v>0</v>
       </c>
       <c r="J201" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K201" s="0" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L201" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M201" s="0" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="N201" s="0" t="n">
         <v>1</v>
@@ -17710,12 +18844,12 @@
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>玄冰斩</t>
+          <t>迎风一刀</t>
         </is>
       </c>
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，1.80×伤害</t>
+          <t>行动每6次，1.4×伤害（外功）</t>
         </is>
       </c>
       <c r="D202" s="0" t="n">
@@ -17728,7 +18862,7 @@
         <v>1</v>
       </c>
       <c r="G202" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H202" s="0" t="n">
         <v>0</v>
@@ -17746,7 +18880,7 @@
         <v>1</v>
       </c>
       <c r="M202" s="0" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="N202" s="0" t="n">
         <v>1</v>
@@ -17794,12 +18928,12 @@
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>孤烟劲</t>
+          <t>双撞撼心捶</t>
         </is>
       </c>
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.70×伤害</t>
+          <t>行动每3次，1.70×伤害（外功）</t>
         </is>
       </c>
       <c r="D203" s="0" t="n">
@@ -17878,12 +19012,12 @@
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>夺魄式</t>
+          <t>排浪掌</t>
         </is>
       </c>
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>行动10%，2.22×内功</t>
+          <t>行动10%，1.33×伤害（内功），敌方全体</t>
         </is>
       </c>
       <c r="D204" s="0" t="n">
@@ -17914,10 +19048,10 @@
         <v>1</v>
       </c>
       <c r="M204" s="0" t="n">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="N204" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O204" s="0" t="b">
         <v>0</v>
@@ -17962,12 +19096,12 @@
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>沉渊踢</t>
+          <t>破浪腿</t>
         </is>
       </c>
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，2.12×伤害</t>
+          <t>行动每6次，2.12×伤害（外功），打敌方血最少</t>
         </is>
       </c>
       <c r="D205" s="0" t="n">
@@ -18001,7 +19135,7 @@
         <v>212</v>
       </c>
       <c r="N205" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O205" s="0" t="b">
         <v>0</v>
@@ -18046,12 +19180,12 @@
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>望月缠</t>
+          <t>六合鞭</t>
         </is>
       </c>
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，3.64×伤害</t>
+          <t>行动每6次，3.64×伤害（外功）；另：目标SPD−12%(10s)</t>
         </is>
       </c>
       <c r="D206" s="0" t="n">
@@ -18122,6 +19256,21 @@
       </c>
       <c r="AA206" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB206" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC206" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD206" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE206" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF206" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -18130,12 +19279,12 @@
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>惊鸿镖</t>
+          <t>没羽箭</t>
         </is>
       </c>
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t>行动25%，2.73×伤害</t>
+          <t>行动每4次，叠毒6层（每层1点/秒，无视护盾，不衰减、无上限）；另：同一次引爆目标毒层（每层0.7×攻击，内功，引爆即清空）</t>
         </is>
       </c>
       <c r="D207" s="0" t="n">
@@ -18145,28 +19294,28 @@
         <v>1</v>
       </c>
       <c r="F207" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G207" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H207" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I207" s="0" t="n">
         <v>0</v>
       </c>
       <c r="J207" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K207" s="0" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L207" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M207" s="0" t="n">
-        <v>273</v>
+        <v>6</v>
       </c>
       <c r="N207" s="0" t="n">
         <v>1</v>
@@ -18206,6 +19355,21 @@
       </c>
       <c r="AA207" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB207" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC207" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD207" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE207" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF207" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -18214,12 +19378,12 @@
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>断桥身法</t>
+          <t>迷踪百变</t>
         </is>
       </c>
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，目标SPD−18%(10s)</t>
+          <t>行动每6次，目标SPD−18%(10s)；另：0.54×伤害（外功）</t>
         </is>
       </c>
       <c r="D208" s="0" t="n">
@@ -18232,7 +19396,7 @@
         <v>1</v>
       </c>
       <c r="G208" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H208" s="0" t="n">
         <v>0</v>
@@ -18290,6 +19454,21 @@
       </c>
       <c r="AA208" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD208" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="AE208" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF208" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -18298,12 +19477,12 @@
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>惊蛰术</t>
+          <t>绝医·回天</t>
         </is>
       </c>
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t>受击每6次，治疗=气血上限9%</t>
+          <t>受击每6次，治疗=气血上限9%；另：护盾=气血上限6%</t>
         </is>
       </c>
       <c r="D209" s="0" t="n">
@@ -18374,6 +19553,21 @@
       </c>
       <c r="AA209" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB209" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC209" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD209" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE209" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF209" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -18382,12 +19576,12 @@
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>清明散</t>
+          <t>无相·淬魂</t>
         </is>
       </c>
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t>受击每5次，给攻击者叠毒1层（层数不衰减，上限5）</t>
+          <t>受击每5次，给攻击者叠毒8层（每层1点/秒，无视护盾，不衰减、无上限）；另：引爆攻击者毒层（每层0.6×攻击，外功，引爆即清空）</t>
         </is>
       </c>
       <c r="D210" s="0" t="n">
@@ -18409,7 +19603,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210" s="0" t="n">
         <v>8</v>
@@ -18418,7 +19612,7 @@
         <v>3</v>
       </c>
       <c r="M210" s="0" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N210" s="0" t="n">
         <v>6</v>
@@ -18458,6 +19652,21 @@
       </c>
       <c r="AA210" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB210" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC210" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD210" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE210" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF210" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -18466,7 +19675,7 @@
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>裂云术</t>
+          <t>招魂幡</t>
         </is>
       </c>
       <c r="C211" s="0" t="inlineStr">
@@ -18555,7 +19764,7 @@
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>飞星禅</t>
+          <t>无念诀</t>
         </is>
       </c>
       <c r="C212" s="0" t="inlineStr">
@@ -18639,12 +19848,12 @@
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>流火爪</t>
+          <t>熊踞镇山</t>
         </is>
       </c>
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，目标ATK−15%(10s)</t>
+          <t>行动每6次，目标ATK−15%(10s)</t>
         </is>
       </c>
       <c r="D213" s="0" t="n">
@@ -18657,7 +19866,7 @@
         <v>1</v>
       </c>
       <c r="G213" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H213" s="0" t="n">
         <v>0</v>
@@ -18723,7 +19932,7 @@
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>碎玉斩</t>
+          <t>空山听雨</t>
         </is>
       </c>
       <c r="C214" s="0" t="inlineStr">
@@ -18807,12 +20016,12 @@
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>赤霄法</t>
+          <t>回身撩月</t>
         </is>
       </c>
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.70×伤害</t>
+          <t>行动每3次，1.70×伤害（外功）</t>
         </is>
       </c>
       <c r="D215" s="0" t="n">
@@ -18891,12 +20100,12 @@
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>长空手</t>
+          <t>卸骨分筋手</t>
         </is>
       </c>
       <c r="C216" s="0" t="inlineStr">
         <is>
-          <t>受击每6次，攻击者ATK−20%(10s)</t>
+          <t>受击每6次，攻击者ATK−20%(10s)；另：0.7×伤害（外功）</t>
         </is>
       </c>
       <c r="D216" s="0" t="n">
@@ -18918,7 +20127,7 @@
         <v>0</v>
       </c>
       <c r="J216" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K216" s="0" t="n">
         <v>7</v>
@@ -18967,6 +20176,21 @@
       </c>
       <c r="AA216" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB216" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC216" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD216" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE216" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF216" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -18975,12 +20199,12 @@
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>刺骨功</t>
+          <t>渡厄掌</t>
         </is>
       </c>
       <c r="C217" s="0" t="inlineStr">
         <is>
-          <t>行动15%，持续治疗=气血上限5.1%/跳(2s)</t>
+          <t>行动15%，HoT 6层（每层1点/2s）；另：每6次，治疗=气血上限7%</t>
         </is>
       </c>
       <c r="D217" s="0" t="n">
@@ -19008,10 +20232,10 @@
         <v>20</v>
       </c>
       <c r="L217" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M217" s="0" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="N217" s="0" t="n">
         <v>0</v>
@@ -19051,6 +20275,21 @@
       </c>
       <c r="AA217" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB217" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC217" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD217" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE217" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF217" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -19059,12 +20298,12 @@
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>焚天步</t>
+          <t>扫堂腿</t>
         </is>
       </c>
       <c r="C218" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，目标SPD−18%(10s)</t>
+          <t>行动每6次，目标SPD−18%(10s)；另：目标W+8(10s)</t>
         </is>
       </c>
       <c r="D218" s="0" t="n">
@@ -19135,6 +20374,21 @@
       </c>
       <c r="AA218" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB218" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC218" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD218" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE218" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF218" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -19143,12 +20397,12 @@
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>疏影索</t>
+          <t>绝鞭·缚龙</t>
         </is>
       </c>
       <c r="C219" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，6.72×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：目标SPD−25%(10s)</t>
         </is>
       </c>
       <c r="D219" s="0" t="n">
@@ -19161,7 +20415,7 @@
         <v>1</v>
       </c>
       <c r="G219" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H219" s="0" t="n">
         <v>0</v>
@@ -19179,7 +20433,7 @@
         <v>1</v>
       </c>
       <c r="M219" s="0" t="n">
-        <v>672</v>
+        <v>588</v>
       </c>
       <c r="N219" s="0" t="n">
         <v>1</v>
@@ -19219,6 +20473,21 @@
       </c>
       <c r="AA219" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB219" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC219" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD219" s="0" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AE219" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF219" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -19227,12 +20496,12 @@
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>振衣手</t>
+          <t>噤声散</t>
         </is>
       </c>
       <c r="C220" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，沉默5s</t>
+          <t>行动每6次，沉默5s；另：同时叠毒8层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D220" s="0" t="n">
@@ -19245,7 +20514,7 @@
         <v>1</v>
       </c>
       <c r="G220" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H220" s="0" t="n">
         <v>0</v>
@@ -19303,6 +20572,21 @@
       </c>
       <c r="AA220" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB220" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC220" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD220" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE220" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF220" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -19311,19 +20595,19 @@
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>穿林影</t>
+          <t>燕回巢</t>
         </is>
       </c>
       <c r="C221" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，完全闪避该次攻击</t>
+          <t>受击每3次，完全闪避该次攻击</t>
         </is>
       </c>
       <c r="D221" s="0" t="n">
         <v>8</v>
       </c>
       <c r="E221" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F221" s="0" t="n">
         <v>1</v>
@@ -19395,12 +20679,12 @@
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>白露经</t>
+          <t>金创诀</t>
         </is>
       </c>
       <c r="C222" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，持续治疗=气血上限1.7%/跳(2s)</t>
+          <t>行动每4次，HoT 2层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D222" s="0" t="n">
@@ -19428,10 +20712,10 @@
         <v>20</v>
       </c>
       <c r="L222" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M222" s="0" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N222" s="0" t="n">
         <v>0</v>
@@ -19479,7 +20763,7 @@
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>谷雨功</t>
+          <t>软筋散</t>
         </is>
       </c>
       <c r="C223" s="0" t="inlineStr">
@@ -19563,12 +20847,12 @@
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>断岳机</t>
+          <t>七星桩</t>
         </is>
       </c>
       <c r="C224" s="0" t="inlineStr">
         <is>
-          <t>行动20%，1.76×内功</t>
+          <t>行动20%，1.76×伤害（内功）</t>
         </is>
       </c>
       <c r="D224" s="0" t="n">
@@ -19647,12 +20931,12 @@
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>落雁印</t>
+          <t>洗髓篇</t>
         </is>
       </c>
       <c r="C225" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，护盾=气血上限16%</t>
+          <t>行动每6次，护盾=气血上限14%</t>
         </is>
       </c>
       <c r="D225" s="0" t="n">
@@ -19665,7 +20949,7 @@
         <v>1</v>
       </c>
       <c r="G225" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H225" s="0" t="n">
         <v>0</v>
@@ -19683,7 +20967,7 @@
         <v>2</v>
       </c>
       <c r="M225" s="0" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N225" s="0" t="n">
         <v>0</v>
@@ -19731,12 +21015,12 @@
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>碎玉形</t>
+          <t>役虎为伥</t>
         </is>
       </c>
       <c r="C226" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，召唤随从</t>
+          <t>行动每6次，召唤随从；另：0.78×伤害（外功）</t>
         </is>
       </c>
       <c r="D226" s="0" t="n">
@@ -19749,7 +21033,7 @@
         <v>1</v>
       </c>
       <c r="G226" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H226" s="0" t="n">
         <v>0</v>
@@ -19812,6 +21096,21 @@
       </c>
       <c r="AA226" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB226" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC226" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD226" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="AE226" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF226" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -19820,19 +21119,19 @@
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>沉沙式</t>
+          <t>千山暮雪</t>
         </is>
       </c>
       <c r="C227" s="0" t="inlineStr">
         <is>
-          <t>行动35%，完全闪避该次攻击</t>
+          <t>受击35%，完全闪避该次攻击；另：每3次，护盾=气血上限4%</t>
         </is>
       </c>
       <c r="D227" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E227" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F227" s="0" t="n">
         <v>2</v>
@@ -19896,6 +21195,21 @@
       </c>
       <c r="AA227" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB227" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC227" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD227" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE227" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF227" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -19904,12 +21218,12 @@
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>苍梧刀</t>
+          <t>八荒断岳</t>
         </is>
       </c>
       <c r="C228" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，反弹累计受击伤害46%</t>
+          <t>行动每4次，反弹累计受击伤害46%（内功）；另：0.9×伤害（外功）</t>
         </is>
       </c>
       <c r="D228" s="0" t="n">
@@ -19980,6 +21294,21 @@
       </c>
       <c r="AA228" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB228" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC228" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD228" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE228" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF228" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -19988,12 +21317,12 @@
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>踏雪拳</t>
+          <t>绝拳·天崩</t>
         </is>
       </c>
       <c r="C229" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，5.25×伤害</t>
+          <t>行动每5次，5.25×伤害（外功）；另：目标ATK−20%(10s)</t>
         </is>
       </c>
       <c r="D229" s="0" t="n">
@@ -20064,6 +21393,21 @@
       </c>
       <c r="AA229" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB229" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC229" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD229" s="0" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AE229" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF229" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -20072,12 +21416,12 @@
       </c>
       <c r="B230" s="0" t="inlineStr">
         <is>
-          <t>锁喉掌</t>
+          <t>绝掌·山河覆</t>
         </is>
       </c>
       <c r="C230" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，5.29×内功</t>
+          <t>行动每6次，5.29×伤害（内功）；另：治疗自身=气血上限8%（以战养战）</t>
         </is>
       </c>
       <c r="D230" s="0" t="n">
@@ -20148,6 +21492,21 @@
       </c>
       <c r="AA230" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB230" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC230" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD230" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE230" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF230" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -20156,12 +21515,12 @@
       </c>
       <c r="B231" s="0" t="inlineStr">
         <is>
-          <t>碎星腿</t>
+          <t>连环踢</t>
         </is>
       </c>
       <c r="C231" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，1.60×伤害</t>
+          <t>行动每5次，敌方全体各挂1层破绽（每层：下一次受击受伤+40%）</t>
         </is>
       </c>
       <c r="D231" s="0" t="n">
@@ -20174,7 +21533,7 @@
         <v>1</v>
       </c>
       <c r="G231" s="0" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H231" s="0" t="n">
         <v>0</v>
@@ -20183,19 +21542,19 @@
         <v>0</v>
       </c>
       <c r="J231" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K231" s="0" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L231" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M231" s="0" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="N231" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O231" s="0" t="b">
         <v>0</v>
@@ -20240,12 +21599,12 @@
       </c>
       <c r="B232" s="0" t="inlineStr">
         <is>
-          <t>暗香鞭</t>
+          <t>绊锋锁足</t>
         </is>
       </c>
       <c r="C232" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，目标W+9(10s)</t>
+          <t>行动每6次，目标W+9(10s)</t>
         </is>
       </c>
       <c r="D232" s="0" t="n">
@@ -20258,7 +21617,7 @@
         <v>1</v>
       </c>
       <c r="G232" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H232" s="0" t="n">
         <v>0</v>
@@ -20324,12 +21683,12 @@
       </c>
       <c r="B233" s="0" t="inlineStr">
         <is>
-          <t>裂帛针</t>
+          <t>三棱刺</t>
         </is>
       </c>
       <c r="C233" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.70×伤害</t>
+          <t>行动每4次，引爆目标毒层（每层0.7×攻击，外功，引爆即清空）</t>
         </is>
       </c>
       <c r="D233" s="0" t="n">
@@ -20342,7 +21701,7 @@
         <v>1</v>
       </c>
       <c r="G233" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H233" s="0" t="n">
         <v>0</v>
@@ -20354,13 +21713,13 @@
         <v>1</v>
       </c>
       <c r="K233" s="0" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L233" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M233" s="0" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="N233" s="0" t="n">
         <v>1</v>
@@ -20408,19 +21767,19 @@
       </c>
       <c r="B234" s="0" t="inlineStr">
         <is>
-          <t>涉川步</t>
+          <t>一叶渡江</t>
         </is>
       </c>
       <c r="C234" s="0" t="inlineStr">
         <is>
-          <t>行动10%，完全闪避该次攻击</t>
+          <t>受击10%，完全闪避该次攻击</t>
         </is>
       </c>
       <c r="D234" s="0" t="n">
         <v>8</v>
       </c>
       <c r="E234" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F234" s="0" t="n">
         <v>2</v>
@@ -20492,7 +21851,7 @@
       </c>
       <c r="B235" s="0" t="inlineStr">
         <is>
-          <t>霜降诀</t>
+          <t>三花聚气</t>
         </is>
       </c>
       <c r="C235" s="0" t="inlineStr">
@@ -20576,12 +21935,12 @@
       </c>
       <c r="B236" s="0" t="inlineStr">
         <is>
-          <t>芒种掌</t>
+          <t>碧蛇丹</t>
         </is>
       </c>
       <c r="C236" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，叠毒1层(每秒0.2×，不衰减，上限5)</t>
+          <t>行动每6次，叠毒6层（每层1点/秒，无视护盾，不衰减、无上限）；另：目标ATK−12%(10s)</t>
         </is>
       </c>
       <c r="D236" s="0" t="n">
@@ -20609,10 +21968,10 @@
         <v>8</v>
       </c>
       <c r="L236" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M236" s="0" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N236" s="0" t="n">
         <v>1</v>
@@ -20652,6 +22011,21 @@
       </c>
       <c r="AA236" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB236" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC236" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD236" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE236" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF236" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -20660,12 +22034,12 @@
       </c>
       <c r="B237" s="0" t="inlineStr">
         <is>
-          <t>寒江阵</t>
+          <t>五鬼役</t>
         </is>
       </c>
       <c r="C237" s="0" t="inlineStr">
         <is>
-          <t>行动25%，召唤随从</t>
+          <t>行动25%，召唤随从；另：每4次，护盾=气血上限6%</t>
         </is>
       </c>
       <c r="D237" s="0" t="n">
@@ -20741,6 +22115,21 @@
       </c>
       <c r="AA237" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB237" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC237" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD237" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE237" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF237" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -20749,12 +22138,12 @@
       </c>
       <c r="B238" s="0" t="inlineStr">
         <is>
-          <t>惊雷功</t>
+          <t>韦陀献杵</t>
         </is>
       </c>
       <c r="C238" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，4.68×伤害</t>
+          <t>行动每6次，伤害=当前护盾×70%（内功，不消耗护盾，需有护盾）；另：护盾=气血上限5%</t>
         </is>
       </c>
       <c r="D238" s="0" t="n">
@@ -20767,7 +22156,7 @@
         <v>1</v>
       </c>
       <c r="G238" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H238" s="0" t="n">
         <v>0</v>
@@ -20776,16 +22165,16 @@
         <v>0</v>
       </c>
       <c r="J238" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K238" s="0" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L238" s="0" t="n">
         <v>1</v>
       </c>
       <c r="M238" s="0" t="n">
-        <v>468</v>
+        <v>70</v>
       </c>
       <c r="N238" s="0" t="n">
         <v>1</v>
@@ -20825,6 +22214,21 @@
       </c>
       <c r="AA238" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB238" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC238" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD238" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE238" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF238" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -20833,12 +22237,12 @@
       </c>
       <c r="B239" s="0" t="inlineStr">
         <is>
-          <t>沉沙诀</t>
+          <t>绝召·万兽行</t>
         </is>
       </c>
       <c r="C239" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，召唤随从</t>
+          <t>行动每3次，召唤随从；另：1.5×伤害（外功，兽群同扑）</t>
         </is>
       </c>
       <c r="D239" s="0" t="n">
@@ -20914,6 +22318,21 @@
       </c>
       <c r="AA239" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB239" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC239" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD239" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="AE239" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF239" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -20922,12 +22341,12 @@
       </c>
       <c r="B240" s="0" t="inlineStr">
         <is>
-          <t>枯木诀</t>
+          <t>无相·寒蝉切</t>
         </is>
       </c>
       <c r="C240" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，4.70×伤害</t>
+          <t>行动每4次，4.70×伤害（外功）；另：行动每2次，0.9×伤害（外功，高频小段）</t>
         </is>
       </c>
       <c r="D240" s="0" t="n">
@@ -20998,6 +22417,21 @@
       </c>
       <c r="AA240" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB240" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC240" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD240" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE240" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF240" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -21006,12 +22440,12 @@
       </c>
       <c r="B241" s="0" t="inlineStr">
         <is>
-          <t>夜雨斩</t>
+          <t>破竹斩</t>
         </is>
       </c>
       <c r="C241" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，消耗全部护盾转化为等量内功伤害</t>
+          <t>行动每3次，给目标挂1层破绽（每层：下一次受击受伤+40%）</t>
         </is>
       </c>
       <c r="D241" s="0" t="n">
@@ -21024,7 +22458,7 @@
         <v>1</v>
       </c>
       <c r="G241" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H241" s="0" t="n">
         <v>0</v>
@@ -21033,10 +22467,10 @@
         <v>0</v>
       </c>
       <c r="J241" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K241" s="0" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="L241" s="0" t="n">
         <v>1</v>
@@ -21045,7 +22479,7 @@
         <v>0</v>
       </c>
       <c r="N241" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241" s="0" t="b">
         <v>0</v>
@@ -21090,12 +22524,12 @@
       </c>
       <c r="B242" s="0" t="inlineStr">
         <is>
-          <t>回风劲</t>
+          <t>寸劲透骨</t>
         </is>
       </c>
       <c r="C242" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，1.40×伤害</t>
+          <t>行动每6次，1.40×伤害（外功）</t>
         </is>
       </c>
       <c r="D242" s="0" t="n">
@@ -21174,12 +22608,12 @@
       </c>
       <c r="B243" s="0" t="inlineStr">
         <is>
-          <t>卷云式</t>
+          <t>三叠浪</t>
         </is>
       </c>
       <c r="C243" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，2.45×内功</t>
+          <t>行动每6次，1.28×伤害（内功），敌方全体</t>
         </is>
       </c>
       <c r="D243" s="0" t="n">
@@ -21192,7 +22626,7 @@
         <v>1</v>
       </c>
       <c r="G243" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H243" s="0" t="n">
         <v>0</v>
@@ -21210,10 +22644,10 @@
         <v>1</v>
       </c>
       <c r="M243" s="0" t="n">
-        <v>245</v>
+        <v>128</v>
       </c>
       <c r="N243" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O243" s="0" t="b">
         <v>0</v>
@@ -21258,7 +22692,7 @@
       </c>
       <c r="B244" s="0" t="inlineStr">
         <is>
-          <t>吞山踢</t>
+          <t>招势踏敌</t>
         </is>
       </c>
       <c r="C244" s="0" t="inlineStr">
@@ -21342,12 +22776,12 @@
       </c>
       <c r="B245" s="0" t="inlineStr">
         <is>
-          <t>落英镖</t>
+          <t>赤蝎尾</t>
         </is>
       </c>
       <c r="C245" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，叠毒1层(每秒0.2×，不衰减，上限5)</t>
+          <t>行动每4次，叠毒6层（每层1点/秒，无视护盾，不衰减、无上限）；另：0.7×伤害（外功）</t>
         </is>
       </c>
       <c r="D245" s="0" t="n">
@@ -21375,10 +22809,10 @@
         <v>8</v>
       </c>
       <c r="L245" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M245" s="0" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N245" s="0" t="n">
         <v>1</v>
@@ -21418,6 +22852,21 @@
       </c>
       <c r="AA245" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB245" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC245" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD245" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE245" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF245" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -21426,12 +22875,12 @@
       </c>
       <c r="B246" s="0" t="inlineStr">
         <is>
-          <t>踏浪身法</t>
+          <t>招风揽敌</t>
         </is>
       </c>
       <c r="C246" s="0" t="inlineStr">
         <is>
-          <t>行动15%，目标W+14(10s)</t>
+          <t>行动15%，目标W+14(10s)；另：每6次，目标SPD−12%(10s)</t>
         </is>
       </c>
       <c r="D246" s="0" t="n">
@@ -21502,6 +22951,21 @@
       </c>
       <c r="AA246" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB246" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC246" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD246" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE246" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF246" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -21510,12 +22974,12 @@
       </c>
       <c r="B247" s="0" t="inlineStr">
         <is>
-          <t>小寒术</t>
+          <t>百草霜</t>
         </is>
       </c>
       <c r="C247" s="0" t="inlineStr">
         <is>
-          <t>受击每5次，护盾=气血上限7.5%</t>
+          <t>受击每5次，护盾=气血上限7.5%；另：治疗=气血上限6%</t>
         </is>
       </c>
       <c r="D247" s="0" t="n">
@@ -21586,6 +23050,21 @@
       </c>
       <c r="AA247" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB247" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC247" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD247" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE247" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF247" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -21594,12 +23073,12 @@
       </c>
       <c r="B248" s="0" t="inlineStr">
         <is>
-          <t>处暑散</t>
+          <t>绝毒·化血</t>
         </is>
       </c>
       <c r="C248" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，灼烧(每秒0.25×，每跳衰减10%%，10s)</t>
+          <t>行动每6次，灼烧12层（每层1点/秒，被护盾吸收，10s）；另：同时叠毒8层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D248" s="0" t="n">
@@ -21612,7 +23091,7 @@
         <v>1</v>
       </c>
       <c r="G248" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H248" s="0" t="n">
         <v>0</v>
@@ -21627,10 +23106,10 @@
         <v>9</v>
       </c>
       <c r="L248" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M248" s="0" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N248" s="0" t="n">
         <v>1</v>
@@ -21670,6 +23149,21 @@
       </c>
       <c r="AA248" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB248" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC248" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD248" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE248" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF248" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -21678,12 +23172,12 @@
       </c>
       <c r="B249" s="0" t="inlineStr">
         <is>
-          <t>孤鸿术</t>
+          <t>八方聚煞</t>
         </is>
       </c>
       <c r="C249" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，目标W+19(10s)</t>
+          <t>行动每6次，目标W+19(10s)；另：附带沉默5s（每场1次）</t>
         </is>
       </c>
       <c r="D249" s="0" t="n">
@@ -21696,7 +23190,7 @@
         <v>1</v>
       </c>
       <c r="G249" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H249" s="0" t="n">
         <v>0</v>
@@ -21754,6 +23248,21 @@
       </c>
       <c r="AA249" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB249" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC249" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE249" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF249" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -21762,7 +23271,7 @@
       </c>
       <c r="B250" s="0" t="inlineStr">
         <is>
-          <t>霜刃禅</t>
+          <t>慈悲手</t>
         </is>
       </c>
       <c r="C250" s="0" t="inlineStr">
@@ -21846,12 +23355,12 @@
       </c>
       <c r="B251" s="0" t="inlineStr">
         <is>
-          <t>枯木爪</t>
+          <t>虎啸扑食</t>
         </is>
       </c>
       <c r="C251" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，1.12×伤害</t>
+          <t>行动每4次，1.12×伤害（外功）</t>
         </is>
       </c>
       <c r="D251" s="0" t="n">
@@ -21930,7 +23439,7 @@
       </c>
       <c r="B252" s="0" t="inlineStr">
         <is>
-          <t>白虹剑</t>
+          <t>示锋引敌</t>
         </is>
       </c>
       <c r="C252" s="0" t="inlineStr">
@@ -22014,12 +23523,12 @@
       </c>
       <c r="B253" s="0" t="inlineStr">
         <is>
-          <t>晓风法</t>
+          <t>卷地风雷</t>
         </is>
       </c>
       <c r="C253" s="0" t="inlineStr">
         <is>
-          <t>行动20%，1.95×伤害</t>
+          <t>行动20%，1.17×伤害（外功），敌方全体</t>
         </is>
       </c>
       <c r="D253" s="0" t="n">
@@ -22050,10 +23559,10 @@
         <v>1</v>
       </c>
       <c r="M253" s="0" t="n">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="N253" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O253" s="0" t="b">
         <v>0</v>
@@ -22098,12 +23607,12 @@
       </c>
       <c r="B254" s="0" t="inlineStr">
         <is>
-          <t>游龙手</t>
+          <t>通天炮</t>
         </is>
       </c>
       <c r="C254" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，反弹累计受击伤害40%</t>
+          <t>行动每6次，反弹累计受击伤害40%（内功）</t>
         </is>
       </c>
       <c r="D254" s="0" t="n">
@@ -22116,7 +23625,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H254" s="0" t="n">
         <v>0</v>
@@ -22182,12 +23691,12 @@
       </c>
       <c r="B255" s="0" t="inlineStr">
         <is>
-          <t>破浪功</t>
+          <t>折锋掌</t>
         </is>
       </c>
       <c r="C255" s="0" t="inlineStr">
         <is>
-          <t>受击每6次，攻击者ATK−20%(10s)</t>
+          <t>受击每6次，攻击者ATK−20%(10s)；另：护盾=气血上限4%</t>
         </is>
       </c>
       <c r="D255" s="0" t="n">
@@ -22258,6 +23767,21 @@
       </c>
       <c r="AA255" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB255" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC255" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD255" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE255" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF255" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -22266,12 +23790,12 @@
       </c>
       <c r="B256" s="0" t="inlineStr">
         <is>
-          <t>听雨步</t>
+          <t>无相·断膝</t>
         </is>
       </c>
       <c r="C256" s="0" t="inlineStr">
         <is>
-          <t>行动35%，2.21×伤害</t>
+          <t>行动35%，2.21×伤害（外功）；另：每3次，目标SPD−12%(10s)（断膝）</t>
         </is>
       </c>
       <c r="D256" s="0" t="n">
@@ -22342,6 +23866,21 @@
       </c>
       <c r="AA256" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB256" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC256" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD256" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE256" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF256" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -22350,12 +23889,12 @@
       </c>
       <c r="B257" s="0" t="inlineStr">
         <is>
-          <t>寒鸦手</t>
+          <t>绝镖·追星</t>
         </is>
       </c>
       <c r="C257" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，5.25×伤害</t>
+          <t>行动每5次，5.25×伤害（外功）；另：引爆目标毒层（每层0.8×攻击，外功，引爆即清空）</t>
         </is>
       </c>
       <c r="D257" s="0" t="n">
@@ -22426,6 +23965,21 @@
       </c>
       <c r="AA257" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB257" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC257" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD257" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE257" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF257" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -22434,12 +23988,12 @@
       </c>
       <c r="B258" s="0" t="inlineStr">
         <is>
-          <t>御风影</t>
+          <t>绝影·踏天</t>
         </is>
       </c>
       <c r="C258" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，5.88×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：附带沉默5s（每场1次）</t>
         </is>
       </c>
       <c r="D258" s="0" t="n">
@@ -22510,6 +24064,21 @@
       </c>
       <c r="AA258" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB258" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC258" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE258" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF258" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -22518,12 +24087,12 @@
       </c>
       <c r="B259" s="0" t="inlineStr">
         <is>
-          <t>大寒经</t>
+          <t>生肌散</t>
         </is>
       </c>
       <c r="C259" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，持续治疗=气血上限2.4%/跳(2s)</t>
+          <t>行动每6次，HoT 2层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D259" s="0" t="n">
@@ -22536,7 +24105,7 @@
         <v>1</v>
       </c>
       <c r="G259" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H259" s="0" t="n">
         <v>0</v>
@@ -22551,10 +24120,10 @@
         <v>20</v>
       </c>
       <c r="L259" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M259" s="0" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="N259" s="0" t="n">
         <v>0</v>
@@ -22602,12 +24171,12 @@
       </c>
       <c r="B260" s="0" t="inlineStr">
         <is>
-          <t>大雪功</t>
+          <t>蚀骨粉</t>
         </is>
       </c>
       <c r="C260" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，叠毒1层(每秒0.2×，不衰减，上限5)</t>
+          <t>行动每6次，叠毒2层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D260" s="0" t="n">
@@ -22620,7 +24189,7 @@
         <v>1</v>
       </c>
       <c r="G260" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H260" s="0" t="n">
         <v>0</v>
@@ -22635,10 +24204,10 @@
         <v>8</v>
       </c>
       <c r="L260" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M260" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N260" s="0" t="n">
         <v>1</v>
@@ -22686,7 +24255,7 @@
       </c>
       <c r="B261" s="0" t="inlineStr">
         <is>
-          <t>残阳机</t>
+          <t>移影换位</t>
         </is>
       </c>
       <c r="C261" s="0" t="inlineStr">
@@ -22770,12 +24339,12 @@
       </c>
       <c r="B262" s="0" t="inlineStr">
         <is>
-          <t>青锋印</t>
+          <t>金刚碎岳杵</t>
         </is>
       </c>
       <c r="C262" s="0" t="inlineStr">
         <is>
-          <t>行动10%，2.46×伤害</t>
+          <t>行动10%，2.46×伤害（外功）</t>
         </is>
       </c>
       <c r="D262" s="0" t="n">
@@ -22854,7 +24423,7 @@
       </c>
       <c r="B263" s="0" t="inlineStr">
         <is>
-          <t>白虹形</t>
+          <t>猿啼引敌</t>
         </is>
       </c>
       <c r="C263" s="0" t="inlineStr">
@@ -22938,12 +24507,12 @@
       </c>
       <c r="B264" s="0" t="inlineStr">
         <is>
-          <t>赤霄斩</t>
+          <t>孤鸿照影</t>
         </is>
       </c>
       <c r="C264" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，2.73×真伤</t>
+          <t>行动每6次，2.73×伤害（真伤）；另：附带沉默5s（每场1次）</t>
         </is>
       </c>
       <c r="D264" s="0" t="n">
@@ -23014,6 +24583,21 @@
       </c>
       <c r="AA264" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB264" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC264" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD264" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF264" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -23022,12 +24606,12 @@
       </c>
       <c r="B265" s="0" t="inlineStr">
         <is>
-          <t>孤烟刀</t>
+          <t>大漠孤烟</t>
         </is>
       </c>
       <c r="C265" s="0" t="inlineStr">
         <is>
-          <t>行动25%，2.73×伤害</t>
+          <t>行动25%，2.73×伤害（外功）；另：每4次，斩杀=目标已损气血15%（外功，每场1次）</t>
         </is>
       </c>
       <c r="D265" s="0" t="n">
@@ -23098,6 +24682,21 @@
       </c>
       <c r="AA265" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB265" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC265" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD265" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE265" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF265" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -23106,12 +24705,12 @@
       </c>
       <c r="B266" s="0" t="inlineStr">
         <is>
-          <t>夺魄拳</t>
+          <t>金刚捣杵</t>
         </is>
       </c>
       <c r="C266" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，4.68×伤害</t>
+          <t>行动每6次，3.64×伤害（外功）；另：自身攻击叠乘+2%/次</t>
         </is>
       </c>
       <c r="D266" s="0" t="n">
@@ -23124,7 +24723,7 @@
         <v>1</v>
       </c>
       <c r="G266" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H266" s="0" t="n">
         <v>0</v>
@@ -23142,7 +24741,7 @@
         <v>1</v>
       </c>
       <c r="M266" s="0" t="n">
-        <v>468</v>
+        <v>364</v>
       </c>
       <c r="N266" s="0" t="n">
         <v>1</v>
@@ -23182,6 +24781,21 @@
       </c>
       <c r="AA266" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB266" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC266" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD266" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF266" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -23190,12 +24804,12 @@
       </c>
       <c r="B267" s="0" t="inlineStr">
         <is>
-          <t>沉渊掌</t>
+          <t>滞空掌</t>
         </is>
       </c>
       <c r="C267" s="0" t="inlineStr">
         <is>
-          <t>受击每7次，攻击者SPD−25%(10s)</t>
+          <t>受击每6次，攻击者SPD−25%(10s)；另：护盾=气血上限6%</t>
         </is>
       </c>
       <c r="D267" s="0" t="n">
@@ -23208,7 +24822,7 @@
         <v>1</v>
       </c>
       <c r="G267" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H267" s="0" t="n">
         <v>0</v>
@@ -23266,6 +24880,21 @@
       </c>
       <c r="AA267" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB267" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC267" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD267" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE267" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF267" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -23274,12 +24903,12 @@
       </c>
       <c r="B268" s="0" t="inlineStr">
         <is>
-          <t>断桥针</t>
+          <t>淬火针</t>
         </is>
       </c>
       <c r="C268" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，灼烧(每秒0.25×，每跳衰减10%%，10s)</t>
+          <t>行动每6次，灼烧3层（每层1点/秒，被护盾吸收，10s）</t>
         </is>
       </c>
       <c r="D268" s="0" t="n">
@@ -23307,10 +24936,10 @@
         <v>9</v>
       </c>
       <c r="L268" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M268" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N268" s="0" t="n">
         <v>1</v>
@@ -23358,7 +24987,7 @@
       </c>
       <c r="B269" s="0" t="inlineStr">
         <is>
-          <t>清明诀</t>
+          <t>当归引</t>
         </is>
       </c>
       <c r="C269" s="0" t="inlineStr">
@@ -23442,12 +25071,12 @@
       </c>
       <c r="B270" s="0" t="inlineStr">
         <is>
-          <t>飞星阵</t>
+          <t>绝阵·八方锁</t>
         </is>
       </c>
       <c r="C270" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，2.62×内功</t>
+          <t>行动每4次，2.62×伤害（内功）；另：附带沉默5s（每场1次）</t>
         </is>
       </c>
       <c r="D270" s="0" t="n">
@@ -23518,6 +25147,21 @@
       </c>
       <c r="AA270" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB270" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC270" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD270" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE270" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF270" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -23526,12 +25170,12 @@
       </c>
       <c r="B271" s="0" t="inlineStr">
         <is>
-          <t>玄冰诀</t>
+          <t>熊形撼山</t>
         </is>
       </c>
       <c r="C271" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，3.64×伤害</t>
+          <t>行动每6次，3.64×伤害（外功）；另：目标SPD−12%(10s)</t>
         </is>
       </c>
       <c r="D271" s="0" t="n">
@@ -23602,6 +25246,21 @@
       </c>
       <c r="AA271" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB271" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC271" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD271" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE271" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF271" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -23610,12 +25269,12 @@
       </c>
       <c r="B272" s="0" t="inlineStr">
         <is>
-          <t>苍梧式</t>
+          <t>绝剑·天外飞锋</t>
         </is>
       </c>
       <c r="C272" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，6.72×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：同一次附带沉默5s（每场1次）</t>
         </is>
       </c>
       <c r="D272" s="0" t="n">
@@ -23628,7 +25287,7 @@
         <v>1</v>
       </c>
       <c r="G272" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H272" s="0" t="n">
         <v>0</v>
@@ -23646,7 +25305,7 @@
         <v>1</v>
       </c>
       <c r="M272" s="0" t="n">
-        <v>672</v>
+        <v>588</v>
       </c>
       <c r="N272" s="0" t="n">
         <v>1</v>
@@ -23686,6 +25345,21 @@
       </c>
       <c r="AA272" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB272" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC272" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD272" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE272" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF272" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -23694,12 +25368,12 @@
       </c>
       <c r="B273" s="0" t="inlineStr">
         <is>
-          <t>长空斩</t>
+          <t>无相·裂帛斩</t>
         </is>
       </c>
       <c r="C273" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，7.56×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：斩杀=目标已损气血19%（外功，每场1次）</t>
         </is>
       </c>
       <c r="D273" s="0" t="n">
@@ -23712,7 +25386,7 @@
         <v>1</v>
       </c>
       <c r="G273" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H273" s="0" t="n">
         <v>0</v>
@@ -23730,7 +25404,7 @@
         <v>1</v>
       </c>
       <c r="M273" s="0" t="n">
-        <v>756</v>
+        <v>588</v>
       </c>
       <c r="N273" s="0" t="n">
         <v>1</v>
@@ -23770,6 +25444,21 @@
       </c>
       <c r="AA273" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB273" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC273" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD273" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE273" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF273" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -23778,12 +25467,12 @@
       </c>
       <c r="B274" s="0" t="inlineStr">
         <is>
-          <t>刺骨劲</t>
+          <t>铁桥靠打</t>
         </is>
       </c>
       <c r="C274" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.00×伤害</t>
+          <t>行动每3次，1.00×伤害（外功）</t>
         </is>
       </c>
       <c r="D274" s="0" t="n">
@@ -23862,12 +25551,12 @@
       </c>
       <c r="B275" s="0" t="inlineStr">
         <is>
-          <t>焚天式</t>
+          <t>铁砂掌</t>
         </is>
       </c>
       <c r="C275" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，1.01×内功</t>
+          <t>行动每4次，1.01×伤害（内功）</t>
         </is>
       </c>
       <c r="D275" s="0" t="n">
@@ -23946,12 +25635,12 @@
       </c>
       <c r="B276" s="0" t="inlineStr">
         <is>
-          <t>穿林镖</t>
+          <t>一叶知秋</t>
         </is>
       </c>
       <c r="C276" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，2.72×伤害</t>
+          <t>行动每5次，叠毒4层（每层1点/秒，无视护盾，不衰减、无上限）</t>
         </is>
       </c>
       <c r="D276" s="0" t="n">
@@ -23964,25 +25653,25 @@
         <v>1</v>
       </c>
       <c r="G276" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H276" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K276" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="H276" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I276" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J276" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K276" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="L276" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M276" s="0" t="n">
-        <v>272</v>
+        <v>4</v>
       </c>
       <c r="N276" s="0" t="n">
         <v>1</v>
@@ -24030,12 +25719,12 @@
       </c>
       <c r="B277" s="0" t="inlineStr">
         <is>
-          <t>谷雨术</t>
+          <t>大还篇</t>
         </is>
       </c>
       <c r="C277" s="0" t="inlineStr">
         <is>
-          <t>受击每6次，护盾=气血上限9%</t>
+          <t>受击每6次，护盾=气血上限9%；另：HoT 6层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D277" s="0" t="n">
@@ -24106,6 +25795,21 @@
       </c>
       <c r="AA277" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB277" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC277" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD277" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE277" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF277" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -24114,12 +25818,12 @@
       </c>
       <c r="B278" s="0" t="inlineStr">
         <is>
-          <t>落雁术</t>
+          <t>锁神阵</t>
         </is>
       </c>
       <c r="C278" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，沉默5s</t>
+          <t>行动每5次，沉默5s；另：目标ATK−20%(10s)</t>
         </is>
       </c>
       <c r="D278" s="0" t="n">
@@ -24190,6 +25894,21 @@
       </c>
       <c r="AA278" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB278" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC278" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD278" s="0" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AE278" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF278" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -24198,12 +25917,12 @@
       </c>
       <c r="B279" s="0" t="inlineStr">
         <is>
-          <t>赤霄爪</t>
+          <t>鹰攫裂帛</t>
         </is>
       </c>
       <c r="C279" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，目标ATK−12%(10s)</t>
+          <t>行动每6次，目标ATK−12%(10s)</t>
         </is>
       </c>
       <c r="D279" s="0" t="n">
@@ -24216,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="G279" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H279" s="0" t="n">
         <v>0</v>
@@ -24282,12 +26001,12 @@
       </c>
       <c r="B280" s="0" t="inlineStr">
         <is>
-          <t>苍梧诀</t>
+          <t>掠影斜挑</t>
         </is>
       </c>
       <c r="C280" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，1.80×伤害</t>
+          <t>行动每6次，1.4×伤害（外功）</t>
         </is>
       </c>
       <c r="D280" s="0" t="n">
@@ -24300,7 +26019,7 @@
         <v>1</v>
       </c>
       <c r="G280" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H280" s="0" t="n">
         <v>0</v>
@@ -24318,7 +26037,7 @@
         <v>1</v>
       </c>
       <c r="M280" s="0" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="N280" s="0" t="n">
         <v>1</v>
@@ -24366,12 +26085,12 @@
       </c>
       <c r="B281" s="0" t="inlineStr">
         <is>
-          <t>踏雪法</t>
+          <t>崩崖裂石</t>
         </is>
       </c>
       <c r="C281" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.70×伤害</t>
+          <t>行动每6次，1.70×伤害（外功），打最高权重</t>
         </is>
       </c>
       <c r="D281" s="0" t="n">
@@ -24405,7 +26124,7 @@
         <v>170</v>
       </c>
       <c r="N281" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O281" s="0" t="b">
         <v>0</v>
@@ -24450,12 +26169,12 @@
       </c>
       <c r="B282" s="0" t="inlineStr">
         <is>
-          <t>锁喉手</t>
+          <t>五雷镇岳</t>
         </is>
       </c>
       <c r="C282" s="0" t="inlineStr">
         <is>
-          <t>行动10%，2.46×伤害</t>
+          <t>行动10%，2.46×伤害（外功）</t>
         </is>
       </c>
       <c r="D282" s="0" t="n">
@@ -24534,12 +26253,12 @@
       </c>
       <c r="B283" s="0" t="inlineStr">
         <is>
-          <t>碎星功</t>
+          <t>六合掌</t>
         </is>
       </c>
       <c r="C283" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，1.91×内功</t>
+          <t>行动每5次，1.91×伤害（内功）</t>
         </is>
       </c>
       <c r="D283" s="0" t="n">
@@ -24618,12 +26337,12 @@
       </c>
       <c r="B284" s="0" t="inlineStr">
         <is>
-          <t>芒种经</t>
+          <t>春生·万木苏</t>
         </is>
       </c>
       <c r="C284" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，治疗=气血上限28%</t>
+          <t>行动每4次，治疗=气血上限28%；另：HoT 8层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D284" s="0" t="n">
@@ -24694,6 +26413,21 @@
       </c>
       <c r="AA284" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB284" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC284" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD284" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE284" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF284" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -24702,7 +26436,7 @@
       </c>
       <c r="B285" s="0" t="inlineStr">
         <is>
-          <t>惊雷机</t>
+          <t>纸马术</t>
         </is>
       </c>
       <c r="C285" s="0" t="inlineStr">
@@ -24791,12 +26525,12 @@
       </c>
       <c r="B286" s="0" t="inlineStr">
         <is>
-          <t>夜雨剑</t>
+          <t>长河饮马</t>
         </is>
       </c>
       <c r="C286" s="0" t="inlineStr">
         <is>
-          <t>行动每3次，1.70×伤害</t>
+          <t>行动每6次，1.70×伤害（外功），打敌方血最少</t>
         </is>
       </c>
       <c r="D286" s="0" t="n">
@@ -24830,7 +26564,7 @@
         <v>170</v>
       </c>
       <c r="N286" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O286" s="0" t="b">
         <v>0</v>
@@ -24875,12 +26609,12 @@
       </c>
       <c r="B287" s="0" t="inlineStr">
         <is>
-          <t>回风刀</t>
+          <t>长河落日</t>
         </is>
       </c>
       <c r="C287" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，2.91×伤害</t>
+          <t>行动每4次，2.91×伤害（外功）；另：目标W+8(10s)（撕开破绽）</t>
         </is>
       </c>
       <c r="D287" s="0" t="n">
@@ -24951,6 +26685,21 @@
       </c>
       <c r="AA287" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB287" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC287" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD287" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE287" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF287" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -24959,12 +26708,12 @@
       </c>
       <c r="B288" s="0" t="inlineStr">
         <is>
-          <t>卷云拳</t>
+          <t>破脉手</t>
         </is>
       </c>
       <c r="C288" s="0" t="inlineStr">
         <is>
-          <t>行动15%，目标ATK−18%(10s)</t>
+          <t>行动15%，目标ATK−18%(10s)；另：每6次，0.75×伤害（外功）</t>
         </is>
       </c>
       <c r="D288" s="0" t="n">
@@ -25035,6 +26784,21 @@
       </c>
       <c r="AA288" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB288" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC288" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD288" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE288" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF288" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -25043,12 +26807,12 @@
       </c>
       <c r="B289" s="0" t="inlineStr">
         <is>
-          <t>吞山掌</t>
+          <t>玉露手</t>
         </is>
       </c>
       <c r="C289" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，持续治疗=气血上限5.5%/跳(2s)</t>
+          <t>行动每6次，HoT 6层（每层1点/2s）；另：治疗=气血上限6%</t>
         </is>
       </c>
       <c r="D289" s="0" t="n">
@@ -25076,10 +26840,10 @@
         <v>20</v>
       </c>
       <c r="L289" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M289" s="0" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="N289" s="0" t="n">
         <v>0</v>
@@ -25119,6 +26883,21 @@
       </c>
       <c r="AA289" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB289" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC289" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD289" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE289" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF289" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -25127,12 +26906,12 @@
       </c>
       <c r="B290" s="0" t="inlineStr">
         <is>
-          <t>处暑诀</t>
+          <t>独活方</t>
         </is>
       </c>
       <c r="C290" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，持续治疗=气血上限3.2%/跳(2s)</t>
+          <t>行动每5次，HoT 4层（每层1点/2s）</t>
         </is>
       </c>
       <c r="D290" s="0" t="n">
@@ -25160,10 +26939,10 @@
         <v>20</v>
       </c>
       <c r="L290" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M290" s="0" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N290" s="0" t="n">
         <v>0</v>
@@ -25211,12 +26990,12 @@
       </c>
       <c r="B291" s="0" t="inlineStr">
         <is>
-          <t>霜刃阵</t>
+          <t>无相·阵杀</t>
         </is>
       </c>
       <c r="C291" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，2.45×内功</t>
+          <t>行动每6次，2.14×伤害（内功）</t>
         </is>
       </c>
       <c r="D291" s="0" t="n">
@@ -25229,7 +27008,7 @@
         <v>1</v>
       </c>
       <c r="G291" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H291" s="0" t="n">
         <v>0</v>
@@ -25247,7 +27026,7 @@
         <v>1</v>
       </c>
       <c r="M291" s="0" t="n">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="N291" s="0" t="n">
         <v>1</v>
@@ -25295,12 +27074,12 @@
       </c>
       <c r="B292" s="0" t="inlineStr">
         <is>
-          <t>晓风斩</t>
+          <t>万里同风</t>
         </is>
       </c>
       <c r="C292" s="0" t="inlineStr">
         <is>
-          <t>行动每4次，2.91×伤害</t>
+          <t>行动每4次，2.91×伤害（外功）；另：目标ATK−12%(10s)</t>
         </is>
       </c>
       <c r="D292" s="0" t="n">
@@ -25371,6 +27150,21 @@
       </c>
       <c r="AA292" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB292" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC292" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD292" s="0" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AE292" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF292" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -25379,12 +27173,12 @@
       </c>
       <c r="B293" s="0" t="inlineStr">
         <is>
-          <t>游龙斩</t>
+          <t>绝刀·山河倾</t>
         </is>
       </c>
       <c r="C293" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，反弹累计受击伤害55%</t>
+          <t>行动每5次，反弹累计受击伤害55%（内功）；另：护盾=气血上限10%（每场2次，先攒后弹）</t>
         </is>
       </c>
       <c r="D293" s="0" t="n">
@@ -25455,6 +27249,21 @@
       </c>
       <c r="AA293" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB293" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC293" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD293" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE293" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF293" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="294">
@@ -25463,12 +27272,12 @@
       </c>
       <c r="B294" s="0" t="inlineStr">
         <is>
-          <t>破浪劲</t>
+          <t>十二路崩</t>
         </is>
       </c>
       <c r="C294" s="0" t="inlineStr">
         <is>
-          <t>行动每6次，5.88×伤害</t>
+          <t>行动每6次，5.88×伤害（外功）；另：行动每2次，0.6×伤害（外功，十二路连崩）</t>
         </is>
       </c>
       <c r="D294" s="0" t="n">
@@ -25539,6 +27348,21 @@
       </c>
       <c r="AA294" s="0" t="n">
         <v>4</v>
+      </c>
+      <c r="AB294" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC294" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD294" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE294" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF294" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -25547,12 +27371,12 @@
       </c>
       <c r="B295" s="0" t="inlineStr">
         <is>
-          <t>听雨式</t>
+          <t>穿心掌</t>
         </is>
       </c>
       <c r="C295" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，1.44×内功</t>
+          <t>行动每6次，1.26×伤害（内功）</t>
         </is>
       </c>
       <c r="D295" s="0" t="n">
@@ -25565,7 +27389,7 @@
         <v>1</v>
       </c>
       <c r="G295" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H295" s="0" t="n">
         <v>0</v>
@@ -25583,7 +27407,7 @@
         <v>1</v>
       </c>
       <c r="M295" s="0" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="N295" s="0" t="n">
         <v>1</v>
@@ -25631,12 +27455,12 @@
       </c>
       <c r="B296" s="0" t="inlineStr">
         <is>
-          <t>青锋术</t>
+          <t>绝召·无常</t>
         </is>
       </c>
       <c r="C296" s="0" t="inlineStr">
         <is>
-          <t>行动每10次，召唤随从</t>
+          <t>行动每6次，召唤随从；另：0.78×伤害（外功）</t>
         </is>
       </c>
       <c r="D296" s="0" t="n">
@@ -25649,7 +27473,7 @@
         <v>1</v>
       </c>
       <c r="G296" s="0" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H296" s="0" t="n">
         <v>0</v>
@@ -25712,6 +27536,21 @@
       </c>
       <c r="AA296" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB296" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC296" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD296" s="0" t="n">
+        <v>78</v>
+      </c>
+      <c r="AE296" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF296" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -25720,19 +27559,19 @@
       </c>
       <c r="B297" s="0" t="inlineStr">
         <is>
-          <t>孤烟式</t>
+          <t>断云截月</t>
         </is>
       </c>
       <c r="C297" s="0" t="inlineStr">
         <is>
-          <t>行动每5次，完全闪避该次攻击</t>
+          <t>受击每5次，完全闪避该次攻击</t>
         </is>
       </c>
       <c r="D297" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E297" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F297" s="0" t="n">
         <v>1</v>
@@ -25804,7 +27643,7 @@
       </c>
       <c r="B298" s="0" t="inlineStr">
         <is>
-          <t>夺魄法</t>
+          <t>劈山断流</t>
         </is>
       </c>
       <c r="C298" s="0" t="inlineStr">
@@ -25888,12 +27727,12 @@
       </c>
       <c r="B299" s="0" t="inlineStr">
         <is>
-          <t>沉渊手</t>
+          <t>破军摧锋</t>
         </is>
       </c>
       <c r="C299" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，2.72×伤害</t>
+          <t>行动每6次，2.38×伤害（外功），打最高权重</t>
         </is>
       </c>
       <c r="D299" s="0" t="n">
@@ -25906,7 +27745,7 @@
         <v>1</v>
       </c>
       <c r="G299" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H299" s="0" t="n">
         <v>0</v>
@@ -25924,10 +27763,10 @@
         <v>1</v>
       </c>
       <c r="M299" s="0" t="n">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="N299" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O299" s="0" t="b">
         <v>0</v>
@@ -25972,12 +27811,12 @@
       </c>
       <c r="B300" s="0" t="inlineStr">
         <is>
-          <t>望月功</t>
+          <t>大悲掌</t>
         </is>
       </c>
       <c r="C300" s="0" t="inlineStr">
         <is>
-          <t>行动30%，1.45×内功</t>
+          <t>行动30%，1.45×伤害（内功）</t>
         </is>
       </c>
       <c r="D300" s="0" t="n">
@@ -26056,7 +27895,7 @@
       </c>
       <c r="B301" s="0" t="inlineStr">
         <is>
-          <t>流火机</t>
+          <t>引煞阵</t>
         </is>
       </c>
       <c r="C301" s="0" t="inlineStr">
@@ -26140,12 +27979,12 @@
       </c>
       <c r="B302" s="0" t="inlineStr">
         <is>
-          <t>长空诀</t>
+          <t>十步一人</t>
         </is>
       </c>
       <c r="C302" s="0" t="inlineStr">
         <is>
-          <t>行动20%，1.95×伤害</t>
+          <t>行动20%，1.95×伤害（外功），打最高权重</t>
         </is>
       </c>
       <c r="D302" s="0" t="n">
@@ -26179,7 +28018,7 @@
         <v>195</v>
       </c>
       <c r="N302" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O302" s="0" t="b">
         <v>0</v>
@@ -26224,12 +28063,12 @@
       </c>
       <c r="B303" s="0" t="inlineStr">
         <is>
-          <t>刺骨刀</t>
+          <t>五丁开山</t>
         </is>
       </c>
       <c r="C303" s="0" t="inlineStr">
         <is>
-          <t>行动每8次，2.72×伤害</t>
+          <t>行动每6次，2.38×伤害（外功），打最高权重</t>
         </is>
       </c>
       <c r="D303" s="0" t="n">
@@ -26242,7 +28081,7 @@
         <v>1</v>
       </c>
       <c r="G303" s="0" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H303" s="0" t="n">
         <v>0</v>
@@ -26260,10 +28099,10 @@
         <v>1</v>
       </c>
       <c r="M303" s="0" t="n">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="N303" s="0" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O303" s="0" t="b">
         <v>0</v>
@@ -26308,12 +28147,12 @@
       </c>
       <c r="B304" s="0" t="inlineStr">
         <is>
-          <t>踏雪剑</t>
+          <t>垂影附骨</t>
         </is>
       </c>
       <c r="C304" s="0" t="inlineStr">
         <is>
-          <t>行动25%，目标W+14(10s)</t>
+          <t>行动25%，目标W+14(10s)；另：每4次，0.8×伤害（外功，标记后追击）</t>
         </is>
       </c>
       <c r="D304" s="0" t="n">
@@ -26384,6 +28223,21 @@
       </c>
       <c r="AA304" s="0" t="n">
         <v>3</v>
+      </c>
+      <c r="AB304" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC304" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD304" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="AE304" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF304" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
